--- a/dados/series/fc27-tango-lobos/dados.xlsx
+++ b/dados/series/fc27-tango-lobos/dados.xlsx
@@ -27,266 +27,284 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="282">
   <si>
     <t>Histórias em Campo — planilha do portal</t>
   </si>
   <si>
+    <t>Episodio</t>
+  </si>
+  <si>
+    <t>Jogo</t>
+  </si>
+  <si>
     <t>Chave</t>
   </si>
   <si>
-    <t>Episodio</t>
+    <t>Temporada</t>
   </si>
   <si>
     <t>COMO USAR</t>
   </si>
   <si>
-    <t>Jogo</t>
+    <t>Titulo</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Link YouTube</t>
+  </si>
+  <si>
+    <t>Resumo</t>
   </si>
   <si>
     <t>1. Cada aba alimenta uma parte do site. Não renomeie as abas nem os títulos das colunas (linha 1).</t>
   </si>
   <si>
+    <t>Competicao</t>
+  </si>
+  <si>
+    <t>Rodada</t>
+  </si>
+  <si>
     <t>2. Preencha a partir da linha 2. Uma linha = um registro. Listas suspensas ajudam nas colunas Local, Competicao, Posicao, Status e Confirmado.</t>
   </si>
   <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Adversario</t>
+  </si>
+  <si>
+    <t>2026/27</t>
+  </si>
+  <si>
+    <t>Descricao</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>CHEGOU o MODO CARREIRA mais REALISTA do YOUTUBE | FC 27 Modo Carreira Realista Wolfsburg| EP 01</t>
+  </si>
+  <si>
+    <t>nome_portal</t>
+  </si>
+  <si>
+    <t>Gols Pro</t>
+  </si>
+  <si>
+    <t>Histórias em Campo</t>
+  </si>
+  <si>
+    <t>Gols Contra</t>
+  </si>
+  <si>
+    <t>Nome exibido no topo do site</t>
+  </si>
+  <si>
     <t>3. Depois de salvar, o site atualiza sozinho (ou envie o arquivo para a pasta 'dados' do site no GitHub com o nome dados.xlsx).</t>
   </si>
   <si>
+    <t>https://www.youtube.com/watch?v=AMmtV3qhNEI</t>
+  </si>
+  <si>
+    <t>clube</t>
+  </si>
+  <si>
+    <t>VfL Wolfsburg</t>
+  </si>
+  <si>
     <t>ABAS</t>
   </si>
   <si>
+    <t>26/27</t>
+  </si>
+  <si>
+    <t>Nome do clube exatamente como aparece na aba Classificacao</t>
+  </si>
+  <si>
+    <t>canal</t>
+  </si>
+  <si>
     <t>Clube — configurações gerais: nome do portal, cores, temporada atual e zonas da tabela (acesso, playoff, rebaixamento).</t>
   </si>
   <si>
+    <t>@gabbiDOMFC</t>
+  </si>
+  <si>
+    <t>Nome do canal</t>
+  </si>
+  <si>
+    <t>link_canal</t>
+  </si>
+  <si>
+    <t>DFB-Pokal</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@gabbiDOMFC</t>
+  </si>
+  <si>
     <t>Episodios — um episódio por linha: número, temporada e um resumo curto. Titulo, Data e Link YouTube podem ficar em branco: o site busca sozinho no canal (vídeos com 'EP 01', 'EP 02'... no título). Se preencher, o que estiver na planilha tem prioridade. A INTRO entra sozinha pelo YouTube.</t>
   </si>
   <si>
-    <t>Valor</t>
+    <t>Link do canal no YouTube</t>
+  </si>
+  <si>
+    <t>1. FC Kaiserslautern</t>
+  </si>
+  <si>
+    <t>temporada_atual</t>
   </si>
   <si>
     <t>Jogos — um jogo por linha, em ordem cronológica. A coluna Jogo é um número sequencial (1, 2, 3...) e é ela que liga os gols ao jogo. O resultado (V/E/D) é calculado pelo site.</t>
   </si>
   <si>
-    <t>Temporada</t>
-  </si>
-  <si>
-    <t>Descricao</t>
+    <t>Casa</t>
+  </si>
+  <si>
+    <t>Temporada mostrada na página inicial</t>
+  </si>
+  <si>
+    <t>competicao_liga</t>
   </si>
   <si>
     <t>Gols — um gol do clube por linha: número do Jogo, Minuto, Autor e Assistencia (deixe vazio se não houve assistência). Minuto é só o número (ex.: 23); nos acréscimos use 45+2 ou 90+3. Para gol contra do adversário, escreva 'Gol contra' em Autor.</t>
   </si>
   <si>
-    <t>Titulo</t>
-  </si>
-  <si>
-    <t>Competicao</t>
-  </si>
-  <si>
-    <t>nome_portal</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>Rodada</t>
+    <t>2. Bundesliga</t>
+  </si>
+  <si>
+    <t>Nome da liga, igual ao usado na aba Jogos</t>
   </si>
   <si>
     <t>Classificacao — a tabela completa ao final de cada episódio (todas as 18 equipes, uma linha cada). Pontos e saldo de gols são calculados pelo site.</t>
   </si>
   <si>
-    <t>Adversario</t>
-  </si>
-  <si>
-    <t>Histórias em Campo</t>
+    <t>cor_primaria</t>
+  </si>
+  <si>
+    <t>#65B32E</t>
   </si>
   <si>
     <t>Elenco — jogadores do elenco com posição e número. Use exatamente os mesmos nomes da aba Gols.</t>
   </si>
   <si>
-    <t>Link YouTube</t>
-  </si>
-  <si>
-    <t>Local</t>
-  </si>
-  <si>
-    <t>Nome exibido no topo do site</t>
-  </si>
-  <si>
-    <t>Resumo</t>
+    <t>Cor principal do site (código hexadecimal)</t>
+  </si>
+  <si>
+    <t>cor_secundaria</t>
   </si>
   <si>
     <t>Recordes — recordes reais do clube até o início da série (temporada 2026/27). NÃO altere a coluna Chave. Edite Valor, Detentor e Quando. Confirmado = SIM tira o aviso 'a confirmar' do site.</t>
   </si>
   <si>
-    <t>Gols Pro</t>
-  </si>
-  <si>
-    <t>Gols Contra</t>
+    <t>#1E4D2B</t>
+  </si>
+  <si>
+    <t>Cor de apoio (fundo do topo)</t>
   </si>
   <si>
     <t>Metas — objetivos da carreira, com Status: Em andamento, Concluída ou Falhou.</t>
   </si>
   <si>
-    <t>clube</t>
-  </si>
-  <si>
-    <t>VfL Wolfsburg</t>
+    <t>escudo</t>
+  </si>
+  <si>
+    <t>Nome do arquivo de imagem do escudo colocado na pasta do site (ex.: escudo.png). Vazio = monograma</t>
   </si>
   <si>
     <t>Titulos — títulos conquistados na carreira (uma linha por título).</t>
   </si>
   <si>
-    <t>Nome do clube exatamente como aparece na aba Classificacao</t>
-  </si>
-  <si>
-    <t>2026/27</t>
+    <t>zona_acesso</t>
   </si>
   <si>
     <t>EXEMPLOS DE PREENCHIMENTO</t>
   </si>
   <si>
-    <t>canal</t>
-  </si>
-  <si>
-    <t>CHEGOU o MODO CARREIRA mais REALISTA do YOUTUBE | FC 27 Modo Carreira Realista Wolfsburg| EP 01</t>
+    <t>Hannover 96</t>
+  </si>
+  <si>
+    <t>Até esta posição: acesso direto</t>
   </si>
   <si>
     <t>Episodios:  1 | 2026/27 | (vazio) | (vazio) | (vazio) | Estreia na 2. Bundesliga com vitória em casa.</t>
   </si>
   <si>
-    <t>@gabbiDOMFC</t>
-  </si>
-  <si>
-    <t>Nome do canal</t>
+    <t>Fora</t>
+  </si>
+  <si>
+    <t>zona_playoff_acesso</t>
+  </si>
+  <si>
+    <t>Posição do playoff de acesso</t>
   </si>
   <si>
     <t>Jogos:  1 | 1 | 2026/27 | 2. Bundesliga | 1 | Hertha BSC | Casa | 2 | 0</t>
   </si>
   <si>
+    <t>Início eletrizante do modo carreira realista com o Wolfsburg agora no comando de um antigo conhecido: Andrés D'Alessandro. Um esboço de time já apresenta gratas surpresas para o decorrer da temporada.</t>
+  </si>
+  <si>
+    <t>zona_playoff_rebaixamento</t>
+  </si>
+  <si>
     <t>Gols:  1 | 34 | Nome do Jogador | Nome de quem deu a assistência</t>
   </si>
   <si>
-    <t>link_canal</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/@gabbiDOMFC</t>
+    <t>Posição do playoff de rebaixamento</t>
   </si>
   <si>
     <t>Classificacao:  1 | 1 | VfL Wolfsburg | 1 | 1 | 0 | 0 | 2 | 0   (Episodio | Posicao | Time | J | V | E | D | GP | GC)</t>
   </si>
   <si>
-    <t>Link do canal no YouTube</t>
+    <t>SÓ TEM RETRANQUEIRO NA SEGUNDA DIVISÃO? | FC 27 Modo Carreira Realista Wolfsburg| EP 02</t>
+  </si>
+  <si>
+    <t>zona_rebaixamento</t>
   </si>
   <si>
     <t>Elenco:  Nome do Jogador | ATA | 9 | Alemanha</t>
   </si>
   <si>
-    <t>temporada_atual</t>
+    <t>Karlsruher SC</t>
+  </si>
+  <si>
+    <t>A partir desta posição: rebaixamento direto</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=eB3sg-pBc1k</t>
+  </si>
+  <si>
+    <t>dados_exemplo</t>
+  </si>
+  <si>
+    <t>NAO</t>
   </si>
   <si>
     <t>ATENÇÃO: os recordes reais estão marcados como 'a confirmar'. Confira cada valor antes de divulgar e mude Confirmado para SIM.</t>
   </si>
   <si>
-    <t>Temporada mostrada na página inicial</t>
-  </si>
-  <si>
-    <t>competicao_liga</t>
-  </si>
-  <si>
-    <t>2. Bundesliga</t>
-  </si>
-  <si>
-    <t>Nome da liga, igual ao usado na aba Jogos</t>
-  </si>
-  <si>
-    <t>cor_primaria</t>
-  </si>
-  <si>
-    <t>#65B32E</t>
-  </si>
-  <si>
-    <t>Cor principal do site (código hexadecimal)</t>
-  </si>
-  <si>
-    <t>cor_secundaria</t>
-  </si>
-  <si>
-    <t>#1E4D2B</t>
-  </si>
-  <si>
-    <t>Cor de apoio (fundo do topo)</t>
-  </si>
-  <si>
-    <t>escudo</t>
-  </si>
-  <si>
-    <t>Nome do arquivo de imagem do escudo colocado na pasta do site (ex.: escudo.png). Vazio = monograma</t>
-  </si>
-  <si>
-    <t>zona_acesso</t>
-  </si>
-  <si>
-    <t>Até esta posição: acesso direto</t>
-  </si>
-  <si>
-    <t>26/27</t>
-  </si>
-  <si>
-    <t>zona_playoff_acesso</t>
-  </si>
-  <si>
-    <t>Posição do playoff de acesso</t>
-  </si>
-  <si>
-    <t>zona_playoff_rebaixamento</t>
-  </si>
-  <si>
-    <t>Posição do playoff de rebaixamento</t>
-  </si>
-  <si>
-    <t>zona_rebaixamento</t>
-  </si>
-  <si>
-    <t>A partir desta posição: rebaixamento direto</t>
-  </si>
-  <si>
-    <t>dados_exemplo</t>
-  </si>
-  <si>
-    <t>DFB-Pokal</t>
-  </si>
-  <si>
-    <t>NAO</t>
-  </si>
-  <si>
     <t>SIM mostra um aviso de dados de exemplo no site</t>
   </si>
   <si>
-    <t>1. FC Kaiserslautern</t>
-  </si>
-  <si>
-    <t>Casa</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=AMmtV3qhNEI</t>
-  </si>
-  <si>
-    <t>Hannover 96</t>
-  </si>
-  <si>
-    <t>Fora</t>
-  </si>
-  <si>
-    <t>Karlsruher SC</t>
-  </si>
-  <si>
     <t>Energie Cottbus</t>
   </si>
   <si>
     <t>FC St. Pauli</t>
   </si>
   <si>
+    <t>D'Alessandro está com dificuldades de enfrentar clubes que acabam joganado de forma mais defensiva. Será que ele consegue encontrar uma solução para furar essas retrancas? Descubra neste episódio.</t>
+  </si>
+  <si>
+    <t>TEMOS um CRISTIANO RONALDO JAPONÊS?! 🐐 | FC 27 Modo Carreira Realista Wolfsburg| EP 03</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=mJnFU4fK3lQ</t>
+  </si>
+  <si>
     <t>SV Darmstadt 98</t>
   </si>
   <si>
@@ -296,98 +314,104 @@
     <t>Heidenheim 1846</t>
   </si>
   <si>
-    <t>Início eletrizante do modo carreira realista com o Wolfsburg agora no comando de um antigo conhecido: Andrés D'Alessandro. Um esboço de time já apresenta gratas surpresas para o decorrer da temporada.</t>
+    <t xml:space="preserve">A sensação japonesa não se cansa de marcar. Será que estamos diante de um CR7 nipônico? </t>
+  </si>
+  <si>
+    <t>O nível SUBIU! Tomamos um AMASSO? | FC 27 Modo Carreira Realista Wolfsburg| EP 04</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=LW1zoO_I704</t>
   </si>
   <si>
     <t>VfL Bochum</t>
   </si>
   <si>
-    <t>SÓ TEM RETRANQUEIRO NA SEGUNDA DIVISÃO? | FC 27 Modo Carreira Realista Wolfsburg| EP 02</t>
-  </si>
-  <si>
     <t>Sport-Club Freiburg</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=eB3sg-pBc1k</t>
+    <t>Os sliders chegaram com tudo, a dificuldade aumentou e nosso time sentiu na pele. Será o fim da boa fase?</t>
+  </si>
+  <si>
+    <t>ELE está nos salvando do PIOR! | FC 27 Modo Carreira Realista Wolfsburg| EP 05</t>
   </si>
   <si>
     <t>VfL Osnabrück</t>
   </si>
   <si>
+    <t>https://www.youtube.com/watch?v=hc248ZsuHh8</t>
+  </si>
+  <si>
     <t>Hertha BSC</t>
   </si>
   <si>
     <t>Holstein Kiel</t>
+  </si>
+  <si>
+    <t>Com os adversários cada vez mais complicados apenas um homem pode nos salvar... Descubra no episódio neste episódio!</t>
+  </si>
+  <si>
+    <t>O WOLFSBURG que vocês conheciam NÃO EXISTE MAIS! | FC 27 Modo Carreira Realista | EP 06</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=N_UrK97rWAQ</t>
   </si>
   <si>
     <t xml:space="preserve">Eintracht Braunschweig
 </t>
   </si>
   <si>
-    <t>D'Alessandro está com dificuldades de enfrentar clubes que acabam joganado de forma mais defensiva. Será que ele consegue encontrar uma solução para furar essas retrancas? Descubra neste episódio.</t>
-  </si>
-  <si>
     <t>1. FC Magdeburg</t>
   </si>
   <si>
-    <t>TEMOS um CRISTIANO RONALDO JAPONÊS?! 🐐 | FC 27 Modo Carreira Realista Wolfsburg| EP 03</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=mJnFU4fK3lQ</t>
-  </si>
-  <si>
     <t>SpVgg Greuther Fürth</t>
   </si>
   <si>
+    <t>O Wolfsburg que vocês conheciam não existe mais. D'Alessandro colocou o cargo à disposição, o clube entrou em crise e só restou um caminho: uma reestruturação completa, dentro e fora de campo. E o primeiro passo pode vir do Uruguai…</t>
+  </si>
+  <si>
     <t>Arminia Bielefeld</t>
   </si>
   <si>
     <t>Dynamo Dresden</t>
   </si>
   <si>
-    <t xml:space="preserve">A sensação japonesa não se cansa de marcar. Será que estamos diante de um CR7 nipônico? </t>
-  </si>
-  <si>
-    <t>O nível SUBIU! Tomamos um AMASSO? | FC 27 Modo Carreira Realista Wolfsburg| EP 04</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=LW1zoO_I704</t>
-  </si>
-  <si>
-    <t>Os sliders chegaram com tudo, a dificuldade aumentou e nosso time sentiu na pele. Será o fim da boa fase?</t>
-  </si>
-  <si>
-    <t>ELE está nos salvando do PIOR! | FC 27 Modo Carreira Realista Wolfsburg| EP 05</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=hc248ZsuHh8</t>
-  </si>
-  <si>
-    <t>Com os adversários cada vez mais complicados apenas um homem pode nos salvar... Descubra no episódio neste episódio!</t>
-  </si>
-  <si>
-    <t>O WOLFSBURG que vocês conheciam NÃO EXISTE MAIS! | FC 27 Modo Carreira Realista | EP 06</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=N_UrK97rWAQ</t>
-  </si>
-  <si>
     <t>Minuto</t>
   </si>
   <si>
+    <t>Posicao</t>
+  </si>
+  <si>
     <t>Autor</t>
   </si>
   <si>
+    <t>Time</t>
+  </si>
+  <si>
     <t>Assistencia</t>
   </si>
   <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>GP</t>
+  </si>
+  <si>
     <t>Damar</t>
   </si>
   <si>
     <t>Shiogai</t>
   </si>
   <si>
-    <t>O Wolfsburg que vocês conheciam não existe mais. D'Alessandro colocou o cargo à disposição, o clube entrou em crise e só restou um caminho: uma reestruturação completa, dentro e fora de campo. E o primeiro passo pode vir do Uruguai…</t>
+    <t>GC</t>
   </si>
   <si>
     <t>Arnold</t>
@@ -414,30 +438,6 @@
     <t>Vinicius Souza</t>
   </si>
   <si>
-    <t>Posicao</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>GP</t>
-  </si>
-  <si>
-    <t>GC</t>
-  </si>
-  <si>
     <t>Jogador</t>
   </si>
   <si>
@@ -459,6 +459,9 @@
     <t>Situacao</t>
   </si>
   <si>
+    <t>Foto</t>
+  </si>
+  <si>
     <t>Grabara</t>
   </si>
   <si>
@@ -525,33 +528,120 @@
     <t>Mæhle</t>
   </si>
   <si>
+    <t>Dinamarca</t>
+  </si>
+  <si>
+    <t>Zehnter</t>
+  </si>
+  <si>
+    <t>LE</t>
+  </si>
+  <si>
+    <t>Rogério</t>
+  </si>
+  <si>
+    <t>VOL</t>
+  </si>
+  <si>
+    <t>Grzywacz</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>Suécia</t>
+  </si>
+  <si>
+    <t>Gerhardt</t>
+  </si>
+  <si>
+    <t>Kosovo</t>
+  </si>
+  <si>
+    <t>Vranckx</t>
+  </si>
+  <si>
+    <t>Bélgica</t>
+  </si>
+  <si>
+    <t>Hensel</t>
+  </si>
+  <si>
+    <t>Dárdai</t>
+  </si>
+  <si>
+    <t>MEI</t>
+  </si>
+  <si>
+    <t>Hungria</t>
+  </si>
+  <si>
+    <t>ATA</t>
+  </si>
+  <si>
+    <t>Benedict</t>
+  </si>
+  <si>
+    <t>PE</t>
+  </si>
+  <si>
+    <t>Amoura</t>
+  </si>
+  <si>
+    <t>Argélia</t>
+  </si>
+  <si>
+    <t>Hornby</t>
+  </si>
+  <si>
+    <t>Escócia</t>
+  </si>
+  <si>
+    <t>Glatzel</t>
+  </si>
+  <si>
+    <t>Japão</t>
+  </si>
+  <si>
+    <t>Besio</t>
+  </si>
+  <si>
+    <t>Suíça</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Emiliano Martínez</t>
+  </si>
+  <si>
+    <t>Uruguai</t>
+  </si>
+  <si>
+    <t>Reforço</t>
+  </si>
+  <si>
+    <t>Till Neininger</t>
+  </si>
+  <si>
+    <t>Andreas Skov Olsen</t>
+  </si>
+  <si>
     <t>Recorde</t>
   </si>
   <si>
-    <t>Dinamarca</t>
-  </si>
-  <si>
     <t>Detentor</t>
   </si>
   <si>
-    <t>Zehnter</t>
-  </si>
-  <si>
     <t>Quando</t>
   </si>
   <si>
-    <t>LE</t>
-  </si>
-  <si>
     <t>Observacao</t>
   </si>
   <si>
     <t>Confirmado</t>
   </si>
   <si>
-    <t>Rogério</t>
-  </si>
-  <si>
     <t>seq_vitorias</t>
   </si>
   <si>
@@ -561,9 +651,6 @@
     <t>Bundesliga 2008/09</t>
   </si>
   <si>
-    <t>VOL</t>
-  </si>
-  <si>
     <t>Sequência da campanha do título alemão</t>
   </si>
   <si>
@@ -573,9 +660,6 @@
     <t>maior_goleada</t>
   </si>
   <si>
-    <t>Grzywacz</t>
-  </si>
-  <si>
     <t>Maior goleada (saldo de gols)</t>
   </si>
   <si>
@@ -588,24 +672,15 @@
     <t>Recorde do clube na competição, confirmado pelo Wolfsburg</t>
   </si>
   <si>
-    <t>MC</t>
-  </si>
-  <si>
     <t>gols_temporada</t>
   </si>
   <si>
-    <t>Suécia</t>
-  </si>
-  <si>
     <t>Mais gols de um jogador numa temporada</t>
   </si>
   <si>
     <t>Grafite</t>
   </si>
   <si>
-    <t>Gerhardt</t>
-  </si>
-  <si>
     <t>Artilheiro da Bundesliga na temporada do título</t>
   </si>
   <si>
@@ -618,40 +693,31 @@
     <t>Kevin De Bruyne</t>
   </si>
   <si>
-    <t>Kosovo</t>
-  </si>
-  <si>
     <t>Bundesliga 2014/15</t>
   </si>
   <si>
     <t>Recorde da Bundesliga na época</t>
   </si>
   <si>
-    <t>Vranckx</t>
-  </si>
-  <si>
     <t>artilheiro_historico</t>
   </si>
   <si>
     <t>Maior artilheiro da história do clube</t>
   </si>
   <si>
-    <t>Bélgica</t>
+    <t>Meta</t>
   </si>
   <si>
     <t>Edin Džeko</t>
   </si>
   <si>
-    <t>Hensel</t>
-  </si>
-  <si>
     <t>2007–2011</t>
   </si>
   <si>
     <t>Gols na Bundesliga</t>
   </si>
   <si>
-    <t>Dárdai</t>
+    <t>Status</t>
   </si>
   <si>
     <t>titulos</t>
@@ -660,73 +726,16 @@
     <t>Títulos de expressão</t>
   </si>
   <si>
-    <t>MEI</t>
-  </si>
-  <si>
-    <t>Hungria</t>
+    <t>Imagem</t>
   </si>
   <si>
     <t>2009–2015</t>
   </si>
   <si>
+    <t>Atual</t>
+  </si>
+  <si>
     <t>Bundesliga 2008/09 · DFB-Pokal 2014/15 · Supercopa da Alemanha 2015</t>
-  </si>
-  <si>
-    <t>ATA</t>
-  </si>
-  <si>
-    <t>Benedict</t>
-  </si>
-  <si>
-    <t>PE</t>
-  </si>
-  <si>
-    <t>Amoura</t>
-  </si>
-  <si>
-    <t>Argélia</t>
-  </si>
-  <si>
-    <t>Hornby</t>
-  </si>
-  <si>
-    <t>Escócia</t>
-  </si>
-  <si>
-    <t>Glatzel</t>
-  </si>
-  <si>
-    <t>Japão</t>
-  </si>
-  <si>
-    <t>Besio</t>
-  </si>
-  <si>
-    <t>Suíça</t>
-  </si>
-  <si>
-    <t>Base</t>
-  </si>
-  <si>
-    <t>Emiliano Martínez</t>
-  </si>
-  <si>
-    <t>Uruguai</t>
-  </si>
-  <si>
-    <t>Reforço</t>
-  </si>
-  <si>
-    <t>Meta</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Imagem</t>
-  </si>
-  <si>
-    <t>Atual</t>
   </si>
   <si>
     <t>Alvo</t>
@@ -895,14 +904,14 @@
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
-      <color rgb="FF2E7D32"/>
+      <sz val="10.0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11.0"/>
+      <color rgb="FF2E7D32"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -965,10 +974,10 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -988,7 +997,7 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1270,76 +1279,76 @@
       <c r="A2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>3</v>
+      <c r="A3" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>8</v>
+      <c r="A8" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
@@ -1347,32 +1356,32 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -1380,7 +1389,7 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1"/>
@@ -2379,14 +2388,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>171</v>
+      <c r="A1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -3391,41 +3400,41 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B3" s="13"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B4" s="14"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B5" s="14"/>
     </row>
@@ -3450,65 +3459,65 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="15" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D1" s="15" t="s">
         <v>136</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="B2" s="6">
         <v>1.0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F2" s="6">
         <v>0.0</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="B3" s="6">
         <v>6.0</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>271</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="F3" s="6">
         <v>1.9E7</v>
@@ -3516,19 +3525,19 @@
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="B4" s="6">
         <v>6.0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F4" s="6">
         <v>7000000.0</v>
@@ -3536,7 +3545,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="B5" s="6">
         <v>6.0</v>
@@ -3545,96 +3554,96 @@
         <v>140</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F5" s="6">
         <v>0.0</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="B6" s="6">
         <v>6.0</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F6" s="6">
         <v>0.0</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="B7" s="6">
         <v>6.0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="B8" s="6">
         <v>6.0</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="B9" s="6">
         <v>6.0</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -3656,115 +3665,115 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>14</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B11" s="5">
         <v>2.0</v>
@@ -3775,46 +3784,46 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B12" s="5">
         <v>3.0</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B13" s="5">
         <v>16.0</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B14" s="5">
         <v>17.0</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -4822,23 +4831,23 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
+      <c r="A1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2">
@@ -4846,19 +4855,19 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="D2" s="7">
         <v>46302.0</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3">
@@ -4866,19 +4875,19 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="D3" s="7">
         <v>46304.0</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4">
@@ -4886,19 +4895,19 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D4" s="7">
         <v>46308.0</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5">
@@ -4906,19 +4915,19 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D5" s="7">
         <v>46311.0</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -4926,19 +4935,19 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D6" s="7">
         <v>46315.0</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7">
@@ -4946,19 +4955,19 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D7" s="11">
         <v>46318.0</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -5977,32 +5986,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>31</v>
+      <c r="D1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2">
@@ -6013,19 +6022,19 @@
         <v>1.0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="E2" s="6">
         <v>1.0</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="H2" s="6">
         <v>4.0</v>
@@ -6042,19 +6051,19 @@
         <v>1.0</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E3" s="6">
         <v>1.0</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="H3" s="6">
         <v>4.0</v>
@@ -6071,19 +6080,19 @@
         <v>1.0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E4" s="6">
         <v>2.0</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="H4" s="6">
         <v>2.0</v>
@@ -6100,19 +6109,19 @@
         <v>1.0</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E5" s="6">
         <v>3.0</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="H5" s="6">
         <v>2.0</v>
@@ -6129,19 +6138,19 @@
         <v>2.0</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E6" s="6">
         <v>4.0</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="H6" s="6">
         <v>2.0</v>
@@ -6158,19 +6167,19 @@
         <v>2.0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E7" s="6">
         <v>5.0</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="H7" s="6">
         <v>0.0</v>
@@ -6187,19 +6196,19 @@
         <v>2.0</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E8" s="6">
         <v>6.0</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="H8" s="6">
         <v>1.0</v>
@@ -6216,19 +6225,19 @@
         <v>2.0</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E9" s="6">
         <v>7.0</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="H9" s="6">
         <v>1.0</v>
@@ -6245,19 +6254,19 @@
         <v>3.0</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E10" s="6">
         <v>8.0</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="H10" s="6">
         <v>4.0</v>
@@ -6274,19 +6283,19 @@
         <v>3.0</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E11" s="6">
         <v>9.0</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="H11" s="6">
         <v>1.0</v>
@@ -6303,19 +6312,19 @@
         <v>3.0</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="E12" s="6">
         <v>2.0</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="H12" s="6">
         <v>0.0</v>
@@ -6332,19 +6341,19 @@
         <v>3.0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E13" s="6">
         <v>10.0</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="H13" s="6">
         <v>5.0</v>
@@ -6361,19 +6370,19 @@
         <v>4.0</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E14" s="6">
         <v>11.0</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="H14" s="6">
         <v>3.0</v>
@@ -6390,19 +6399,19 @@
         <v>4.0</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E15" s="6">
         <v>12.0</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="H15" s="6">
         <v>1.0</v>
@@ -6419,19 +6428,19 @@
         <v>4.0</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E16" s="6">
         <v>13.0</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="H16" s="6">
         <v>1.0</v>
@@ -6448,19 +6457,19 @@
         <v>5.0</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E17" s="6">
         <v>14.0</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="H17" s="6">
         <v>1.0</v>
@@ -6477,19 +6486,19 @@
         <v>5.0</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E18" s="6">
         <v>15.0</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="H18" s="6">
         <v>2.0</v>
@@ -6506,19 +6515,19 @@
         <v>5.0</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E19" s="6">
         <v>16.0</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="H19" s="6">
         <v>2.0</v>
@@ -6535,19 +6544,19 @@
         <v>6.0</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E20" s="6">
         <v>17.0</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="H20" s="6">
         <v>1.0</v>
@@ -6564,19 +6573,19 @@
         <v>6.0</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E21" s="6">
         <v>18.0</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="H21" s="6">
         <v>2.0</v>
@@ -6593,19 +6602,19 @@
         <v>6.0</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E22" s="6">
         <v>19.0</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="H22" s="6">
         <v>2.0</v>
@@ -10556,17 +10565,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>116</v>
+      <c r="C1" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="2">
@@ -10577,10 +10586,10 @@
         <v>33.0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3">
@@ -10591,10 +10600,10 @@
         <v>38.0</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4">
@@ -10605,10 +10614,10 @@
         <v>50.0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5">
@@ -10619,10 +10628,10 @@
         <v>57.0</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6">
@@ -10633,10 +10642,10 @@
         <v>17.0</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7">
@@ -10647,10 +10656,10 @@
         <v>42.0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8">
@@ -10661,7 +10670,7 @@
         <v>59.0</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9">
@@ -10672,10 +10681,10 @@
         <v>86.0</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10">
@@ -10686,10 +10695,10 @@
         <v>28.0</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11">
@@ -10700,7 +10709,7 @@
         <v>53.0</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12">
@@ -10711,10 +10720,10 @@
         <v>45.0</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -10725,10 +10734,10 @@
         <v>82.0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14">
@@ -10739,10 +10748,10 @@
         <v>8.0</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15">
@@ -10753,10 +10762,10 @@
         <v>80.0</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16">
@@ -10767,10 +10776,10 @@
         <v>75.0</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17">
@@ -10781,10 +10790,10 @@
         <v>73.0</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18">
@@ -10795,10 +10804,10 @@
         <v>28.0</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19">
@@ -10809,10 +10818,10 @@
         <v>35.0</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20">
@@ -10823,10 +10832,10 @@
         <v>40.0</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -10837,10 +10846,10 @@
         <v>88.0</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -10851,10 +10860,10 @@
         <v>28.0</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -10865,10 +10874,10 @@
         <v>27.0</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -10879,10 +10888,10 @@
         <v>37.0</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -10893,10 +10902,10 @@
         <v>39.0</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -10907,10 +10916,10 @@
         <v>56.0</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
@@ -10921,10 +10930,10 @@
         <v>69.0</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -10935,10 +10944,10 @@
         <v>4.0</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -10949,10 +10958,10 @@
         <v>7.0</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -10963,10 +10972,10 @@
         <v>39.0</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
@@ -10977,10 +10986,10 @@
         <v>59.0</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
@@ -10991,10 +11000,10 @@
         <v>82.0</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
@@ -11005,10 +11014,10 @@
         <v>47.0</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
@@ -11019,10 +11028,10 @@
         <v>3.0</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
@@ -11033,10 +11042,10 @@
         <v>63.0</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
@@ -11047,10 +11056,10 @@
         <v>74.0</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
@@ -11061,10 +11070,10 @@
         <v>82.0</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
@@ -11075,10 +11084,10 @@
         <v>83.0</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
@@ -11089,10 +11098,10 @@
         <v>51.0</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
@@ -11103,10 +11112,10 @@
         <v>71.0</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
@@ -11117,10 +11126,10 @@
         <v>20.0</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
@@ -11131,10 +11140,10 @@
         <v>84.0</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1"/>
@@ -12118,32 +12127,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>135</v>
+      <c r="A1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="2">
@@ -12154,7 +12163,7 @@
         <v>1.0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D2" s="6">
         <v>19.0</v>
@@ -12183,7 +12192,7 @@
         <v>2.0</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D3" s="6">
         <v>19.0</v>
@@ -12212,7 +12221,7 @@
         <v>3.0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="D4" s="6">
         <v>18.0</v>
@@ -12241,7 +12250,7 @@
         <v>4.0</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="D5" s="6">
         <v>19.0</v>
@@ -12270,7 +12279,7 @@
         <v>5.0</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D6" s="6">
         <v>19.0</v>
@@ -12299,7 +12308,7 @@
         <v>6.0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D7" s="6">
         <v>19.0</v>
@@ -13331,7 +13340,7 @@
         <v>136</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C1" s="12" t="s">
         <v>137</v>
@@ -13351,459 +13360,462 @@
       <c r="H1" s="6" t="s">
         <v>142</v>
       </c>
+      <c r="I1" s="6" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>154</v>
-      </c>
       <c r="D7" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>160</v>
-      </c>
       <c r="E10" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>162</v>
-      </c>
       <c r="D11" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>166</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>170</v>
-      </c>
       <c r="D13" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>211</v>
+        <v>181</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="6" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="6" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="6" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="6" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>222</v>
+        <v>190</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>224</v>
+        <v>192</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="6" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="F33" s="6">
         <v>3.0</v>
@@ -13811,26 +13823,54 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="6" t="s">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>227</v>
+        <v>195</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>228</v>
+        <v>196</v>
       </c>
       <c r="F34" s="6">
         <v>6.0</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="B35" s="5"/>
+      <c r="A35" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="B36" s="5"/>
+      <c r="A36" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="B37" s="5"/>
@@ -15147,163 +15187,163 @@
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C2" s="6">
         <v>10.0</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="C3" s="6">
         <v>9.0</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>183</v>
+        <v>211</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>184</v>
+        <v>212</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="C4" s="6">
         <v>28.0</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="C5" s="6">
         <v>20.0</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="C6" s="6">
         <v>66.0</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="C7" s="6">
         <v>3.0</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8">
@@ -16519,96 +16559,96 @@
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>230</v>
-      </c>
       <c r="C1" s="12" t="s">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E5" s="6">
         <v>2.0</v>
@@ -16617,72 +16657,72 @@
         <v>5.0</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="6" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="6" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D8" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="H8" s="6" t="s">
         <v>259</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="6" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">

--- a/dados/series/fc27-tango-lobos/dados.xlsx
+++ b/dados/series/fc27-tango-lobos/dados.xlsx
@@ -27,242 +27,242 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="296">
   <si>
     <t>Histórias em Campo — planilha do portal</t>
   </si>
   <si>
+    <t>Chave</t>
+  </si>
+  <si>
+    <t>Episodio</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Descricao</t>
+  </si>
+  <si>
     <t>COMO USAR</t>
   </si>
   <si>
+    <t>nome_portal</t>
+  </si>
+  <si>
+    <t>Temporada</t>
+  </si>
+  <si>
     <t>1. Cada aba alimenta uma parte do site. Não renomeie as abas nem os títulos das colunas (linha 1).</t>
   </si>
   <si>
+    <t>Histórias em Campo</t>
+  </si>
+  <si>
+    <t>Titulo</t>
+  </si>
+  <si>
     <t>2. Preencha a partir da linha 2. Uma linha = um registro. Listas suspensas ajudam nas colunas Local, Competicao, Posicao, Status e Confirmado.</t>
   </si>
   <si>
+    <t>Jogo</t>
+  </si>
+  <si>
     <t>3. Depois de salvar, o site atualiza sozinho (ou envie o arquivo para a pasta 'dados' do site no GitHub com o nome dados.xlsx).</t>
   </si>
   <si>
+    <t>Nome exibido no topo do site</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Link YouTube</t>
+  </si>
+  <si>
     <t>ABAS</t>
   </si>
   <si>
+    <t>clube</t>
+  </si>
+  <si>
+    <t>Resumo</t>
+  </si>
+  <si>
+    <t>VfL Wolfsburg</t>
+  </si>
+  <si>
     <t>Clube — configurações gerais: nome do portal, cores, temporada atual e zonas da tabela (acesso, playoff, rebaixamento).</t>
   </si>
   <si>
+    <t>Nome do clube exatamente como aparece na aba Classificacao</t>
+  </si>
+  <si>
+    <t>canal</t>
+  </si>
+  <si>
     <t>Episodios — um episódio por linha: número, temporada e um resumo curto. Titulo, Data e Link YouTube podem ficar em branco: o site busca sozinho no canal (vídeos com 'EP 01', 'EP 02'... no título). Se preencher, o que estiver na planilha tem prioridade. A INTRO entra sozinha pelo YouTube.</t>
   </si>
   <si>
+    <t>2026/27</t>
+  </si>
+  <si>
+    <t>Competicao</t>
+  </si>
+  <si>
+    <t>@gabbiDOMFC</t>
+  </si>
+  <si>
+    <t>Nome do canal</t>
+  </si>
+  <si>
+    <t>Rodada</t>
+  </si>
+  <si>
+    <t>CHEGOU o MODO CARREIRA mais REALISTA do YOUTUBE | FC 27 Modo Carreira Realista Wolfsburg| EP 01</t>
+  </si>
+  <si>
     <t>Jogos — um jogo por linha, em ordem cronológica. A coluna Jogo é um número sequencial (1, 2, 3...) e é ela que liga os gols ao jogo. O resultado (V/E/D) é calculado pelo site.</t>
   </si>
   <si>
+    <t>link_canal</t>
+  </si>
+  <si>
+    <t>Adversario</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@gabbiDOMFC</t>
+  </si>
+  <si>
     <t>Gols — um gol do clube por linha: número do Jogo, Minuto, Autor e Assistencia (deixe vazio se não houve assistência). Minuto é só o número (ex.: 23); nos acréscimos use 45+2 ou 90+3. Para gol contra do adversário, escreva 'Gol contra' em Autor.</t>
   </si>
   <si>
+    <t>Link do canal no YouTube</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
     <t>Classificacao — a tabela completa ao final de cada episódio (todas as 18 equipes, uma linha cada). Pontos e saldo de gols são calculados pelo site.</t>
   </si>
   <si>
+    <t>temporada_atual</t>
+  </si>
+  <si>
+    <t>Gols Pro</t>
+  </si>
+  <si>
     <t>Elenco — jogadores do elenco com posição e número. Use exatamente os mesmos nomes da aba Gols.</t>
   </si>
   <si>
+    <t>Gols Contra</t>
+  </si>
+  <si>
+    <t>Temporada mostrada na página inicial</t>
+  </si>
+  <si>
     <t>Recordes — recordes reais do clube até o início da série (temporada 2026/27). NÃO altere a coluna Chave. Edite Valor, Detentor e Quando. Confirmado = SIM tira o aviso 'a confirmar' do site.</t>
   </si>
   <si>
-    <t>Chave</t>
+    <t>competicao_liga</t>
   </si>
   <si>
     <t>Metas — objetivos da carreira, com Status: Em andamento, Concluída ou Falhou.</t>
   </si>
   <si>
+    <t>2. Bundesliga</t>
+  </si>
+  <si>
+    <t>Nome da liga, igual ao usado na aba Jogos</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=AMmtV3qhNEI</t>
+  </si>
+  <si>
     <t>Titulos — títulos conquistados na carreira (uma linha por título).</t>
   </si>
   <si>
+    <t>26/27</t>
+  </si>
+  <si>
+    <t>cor_primaria</t>
+  </si>
+  <si>
+    <t>#65B32E</t>
+  </si>
+  <si>
     <t>EXEMPLOS DE PREENCHIMENTO</t>
   </si>
   <si>
+    <t>Cor principal do site (código hexadecimal)</t>
+  </si>
+  <si>
     <t>Episodios:  1 | 2026/27 | (vazio) | (vazio) | (vazio) | Estreia na 2. Bundesliga com vitória em casa.</t>
   </si>
   <si>
+    <t>cor_secundaria</t>
+  </si>
+  <si>
+    <t>#1E4D2B</t>
+  </si>
+  <si>
+    <t>Cor de apoio (fundo do topo)</t>
+  </si>
+  <si>
     <t>Jogos:  1 | 1 | 2026/27 | 2. Bundesliga | 1 | Hertha BSC | Casa | 2 | 0</t>
   </si>
   <si>
+    <t>escudo</t>
+  </si>
+  <si>
+    <t>Nome do arquivo de imagem do escudo colocado na pasta do site (ex.: escudo.png). Vazio = monograma</t>
+  </si>
+  <si>
     <t>Gols:  1 | 34 | Nome do Jogador | Nome de quem deu a assistência</t>
   </si>
   <si>
-    <t>Valor</t>
-  </si>
-  <si>
-    <t>Descricao</t>
+    <t>DFB-Pokal</t>
+  </si>
+  <si>
+    <t>zona_acesso</t>
   </si>
   <si>
     <t>Classificacao:  1 | 1 | VfL Wolfsburg | 1 | 1 | 0 | 0 | 2 | 0   (Episodio | Posicao | Time | J | V | E | D | GP | GC)</t>
   </si>
   <si>
+    <t>1. FC Kaiserslautern</t>
+  </si>
+  <si>
+    <t>Até esta posição: acesso direto</t>
+  </si>
+  <si>
     <t>Elenco:  Nome do Jogador | ATA | 9 | Alemanha</t>
   </si>
   <si>
-    <t>nome_portal</t>
+    <t>zona_playoff_acesso</t>
+  </si>
+  <si>
+    <t>Casa</t>
+  </si>
+  <si>
+    <t>Posição do playoff de acesso</t>
   </si>
   <si>
     <t>ATENÇÃO: os recordes reais estão marcados como 'a confirmar'. Confira cada valor antes de divulgar e mude Confirmado para SIM.</t>
   </si>
   <si>
-    <t>Histórias em Campo</t>
-  </si>
-  <si>
-    <t>Nome exibido no topo do site</t>
-  </si>
-  <si>
-    <t>Episodio</t>
-  </si>
-  <si>
-    <t>clube</t>
-  </si>
-  <si>
-    <t>VfL Wolfsburg</t>
-  </si>
-  <si>
-    <t>Nome do clube exatamente como aparece na aba Classificacao</t>
-  </si>
-  <si>
-    <t>Temporada</t>
-  </si>
-  <si>
-    <t>canal</t>
-  </si>
-  <si>
-    <t>Jogo</t>
-  </si>
-  <si>
-    <t>@gabbiDOMFC</t>
-  </si>
-  <si>
-    <t>Nome do canal</t>
-  </si>
-  <si>
-    <t>Titulo</t>
-  </si>
-  <si>
-    <t>link_canal</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/@gabbiDOMFC</t>
-  </si>
-  <si>
-    <t>Link do canal no YouTube</t>
-  </si>
-  <si>
-    <t>Link YouTube</t>
-  </si>
-  <si>
-    <t>temporada_atual</t>
-  </si>
-  <si>
-    <t>2026/27</t>
-  </si>
-  <si>
-    <t>Resumo</t>
-  </si>
-  <si>
-    <t>Competicao</t>
-  </si>
-  <si>
-    <t>Temporada mostrada na página inicial</t>
-  </si>
-  <si>
-    <t>Rodada</t>
-  </si>
-  <si>
-    <t>competicao_liga</t>
-  </si>
-  <si>
-    <t>2. Bundesliga</t>
-  </si>
-  <si>
-    <t>Adversario</t>
-  </si>
-  <si>
-    <t>Nome da liga, igual ao usado na aba Jogos</t>
-  </si>
-  <si>
-    <t>Local</t>
-  </si>
-  <si>
-    <t>cor_primaria</t>
-  </si>
-  <si>
-    <t>Gols Pro</t>
-  </si>
-  <si>
-    <t>#65B32E</t>
-  </si>
-  <si>
-    <t>Gols Contra</t>
-  </si>
-  <si>
-    <t>CHEGOU o MODO CARREIRA mais REALISTA do YOUTUBE | FC 27 Modo Carreira Realista Wolfsburg| EP 01</t>
-  </si>
-  <si>
-    <t>Cor principal do site (código hexadecimal)</t>
-  </si>
-  <si>
-    <t>cor_secundaria</t>
-  </si>
-  <si>
-    <t>#1E4D2B</t>
-  </si>
-  <si>
-    <t>Cor de apoio (fundo do topo)</t>
-  </si>
-  <si>
-    <t>escudo</t>
-  </si>
-  <si>
-    <t>Nome do arquivo de imagem do escudo colocado na pasta do site (ex.: escudo.png). Vazio = monograma</t>
-  </si>
-  <si>
-    <t>26/27</t>
-  </si>
-  <si>
-    <t>zona_acesso</t>
-  </si>
-  <si>
-    <t>Até esta posição: acesso direto</t>
-  </si>
-  <si>
-    <t>zona_playoff_acesso</t>
-  </si>
-  <si>
-    <t>Posição do playoff de acesso</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=AMmtV3qhNEI</t>
-  </si>
-  <si>
-    <t>DFB-Pokal</t>
-  </si>
-  <si>
     <t>zona_playoff_rebaixamento</t>
   </si>
   <si>
     <t>Posição do playoff de rebaixamento</t>
   </si>
   <si>
-    <t>1. FC Kaiserslautern</t>
-  </si>
-  <si>
     <t>zona_rebaixamento</t>
   </si>
   <si>
     <t>A partir desta posição: rebaixamento direto</t>
   </si>
   <si>
-    <t>Casa</t>
-  </si>
-  <si>
     <t>dados_exemplo</t>
   </si>
   <si>
@@ -281,24 +281,24 @@
     <t>Karlsruher SC</t>
   </si>
   <si>
+    <t>Início eletrizante do modo carreira realista com o Wolfsburg agora no comando de um antigo conhecido: Andrés D'Alessandro. Um esboço de time já apresenta gratas surpresas para o decorrer da temporada.</t>
+  </si>
+  <si>
+    <t>SÓ TEM RETRANQUEIRO NA SEGUNDA DIVISÃO? | FC 27 Modo Carreira Realista Wolfsburg| EP 02</t>
+  </si>
+  <si>
     <t>Energie Cottbus</t>
   </si>
   <si>
+    <t>https://www.youtube.com/watch?v=eB3sg-pBc1k</t>
+  </si>
+  <si>
     <t>FC St. Pauli</t>
   </si>
   <si>
-    <t>Início eletrizante do modo carreira realista com o Wolfsburg agora no comando de um antigo conhecido: Andrés D'Alessandro. Um esboço de time já apresenta gratas surpresas para o decorrer da temporada.</t>
-  </si>
-  <si>
     <t>SV Darmstadt 98</t>
   </si>
   <si>
-    <t>SÓ TEM RETRANQUEIRO NA SEGUNDA DIVISÃO? | FC 27 Modo Carreira Realista Wolfsburg| EP 02</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=eB3sg-pBc1k</t>
-  </si>
-  <si>
     <t>1. FC Nürnberg</t>
   </si>
   <si>
@@ -308,31 +308,40 @@
     <t>VfL Bochum</t>
   </si>
   <si>
+    <t>D'Alessandro está com dificuldades de enfrentar clubes que acabam joganado de forma mais defensiva. Será que ele consegue encontrar uma solução para furar essas retrancas? Descubra neste episódio.</t>
+  </si>
+  <si>
     <t>Sport-Club Freiburg</t>
   </si>
   <si>
+    <t>TEMOS um CRISTIANO RONALDO JAPONÊS?! 🐐 | FC 27 Modo Carreira Realista Wolfsburg| EP 03</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=mJnFU4fK3lQ</t>
+  </si>
+  <si>
     <t>VfL Osnabrück</t>
   </si>
   <si>
-    <t>D'Alessandro está com dificuldades de enfrentar clubes que acabam joganado de forma mais defensiva. Será que ele consegue encontrar uma solução para furar essas retrancas? Descubra neste episódio.</t>
-  </si>
-  <si>
-    <t>TEMOS um CRISTIANO RONALDO JAPONÊS?! 🐐 | FC 27 Modo Carreira Realista Wolfsburg| EP 03</t>
-  </si>
-  <si>
     <t>Hertha BSC</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=mJnFU4fK3lQ</t>
-  </si>
-  <si>
     <t>Holstein Kiel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A sensação japonesa não se cansa de marcar. Será que estamos diante de um CR7 nipônico? </t>
   </si>
   <si>
     <t xml:space="preserve">Eintracht Braunschweig
 </t>
   </si>
   <si>
+    <t>O nível SUBIU! Tomamos um AMASSO? | FC 27 Modo Carreira Realista Wolfsburg| EP 04</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=LW1zoO_I704</t>
+  </si>
+  <si>
     <t>1. FC Magdeburg</t>
   </si>
   <si>
@@ -342,16 +351,25 @@
     <t>Arminia Bielefeld</t>
   </si>
   <si>
-    <t xml:space="preserve">A sensação japonesa não se cansa de marcar. Será que estamos diante de um CR7 nipônico? </t>
-  </si>
-  <si>
-    <t>O nível SUBIU! Tomamos um AMASSO? | FC 27 Modo Carreira Realista Wolfsburg| EP 04</t>
+    <t>Os sliders chegaram com tudo, a dificuldade aumentou e nosso time sentiu na pele. Será o fim da boa fase?</t>
   </si>
   <si>
     <t>Dynamo Dresden</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=LW1zoO_I704</t>
+    <t>ELE está nos salvando do PIOR! | FC 27 Modo Carreira Realista Wolfsburg| EP 05</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=hc248ZsuHh8</t>
+  </si>
+  <si>
+    <t>Com os adversários cada vez mais complicados apenas um homem pode nos salvar... Descubra no episódio neste episódio!</t>
+  </si>
+  <si>
+    <t>O WOLFSBURG que vocês conheciam NÃO EXISTE MAIS! | FC 27 Modo Carreira Realista | EP 06</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=N_UrK97rWAQ</t>
   </si>
   <si>
     <t>Minuto</t>
@@ -367,45 +385,6 @@
   </si>
   <si>
     <t>Shiogai</t>
-  </si>
-  <si>
-    <t>Os sliders chegaram com tudo, a dificuldade aumentou e nosso time sentiu na pele. Será o fim da boa fase?</t>
-  </si>
-  <si>
-    <t>ELE está nos salvando do PIOR! | FC 27 Modo Carreira Realista Wolfsburg| EP 05</t>
-  </si>
-  <si>
-    <t>Arnold</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=hc248ZsuHh8</t>
-  </si>
-  <si>
-    <t>Reese</t>
-  </si>
-  <si>
-    <t>Bernhardsson</t>
-  </si>
-  <si>
-    <t>Svanberg</t>
-  </si>
-  <si>
-    <t>Com os adversários cada vez mais complicados apenas um homem pode nos salvar... Descubra no episódio neste episódio!</t>
-  </si>
-  <si>
-    <t>O WOLFSBURG que vocês conheciam NÃO EXISTE MAIS! | FC 27 Modo Carreira Realista | EP 06</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=N_UrK97rWAQ</t>
-  </si>
-  <si>
-    <t>Rexhbeçaj</t>
-  </si>
-  <si>
-    <t>Dardai</t>
-  </si>
-  <si>
-    <t>Winkler</t>
   </si>
   <si>
     <t>O Wolfsburg que vocês conheciam não existe mais. D'Alessandro colocou o cargo à disposição, o clube entrou em crise e só restou um caminho: uma reestruturação completa, dentro e fora de campo. E o primeiro passo pode vir do Uruguai…</t>
@@ -415,39 +394,60 @@
 </t>
   </si>
   <si>
+    <t>Arnold</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=lZ5DxuA-Jms&amp;t=1399s</t>
   </si>
   <si>
+    <t>Reese</t>
+  </si>
+  <si>
+    <t>Bernhardsson</t>
+  </si>
+  <si>
+    <t>Svanberg</t>
+  </si>
+  <si>
+    <t>Faltando poucas horas pro fim da janela, o Barcelona ligou. Eles queriam o nosso artilheiro. Entre 4 reforços chegando e uma decisão que pode mudar a temporada inteira, o novo Wolfsburg começa a tomar forma no nosso Modo Carreira Realista do FC 27.</t>
+  </si>
+  <si>
+    <t>Posicao</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>GP</t>
+  </si>
+  <si>
+    <t>GC</t>
+  </si>
+  <si>
+    <t>Rexhbeçaj</t>
+  </si>
+  <si>
+    <t>Dardai</t>
+  </si>
+  <si>
+    <t>Winkler</t>
+  </si>
+  <si>
     <t>Vinicius Souza</t>
   </si>
   <si>
-    <t>Faltando poucas horas pro fim da janela, o Barcelona ligou. Eles queriam o nosso artilheiro. Entre 4 reforços chegando e uma decisão que pode mudar a temporada inteira, o novo Wolfsburg começa a tomar forma no nosso Modo Carreira Realista do FC 27.</t>
-  </si>
-  <si>
-    <t>Posicao</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>GP</t>
-  </si>
-  <si>
-    <t>GC</t>
-  </si>
-  <si>
     <t>Jogador</t>
   </si>
   <si>
@@ -475,54 +475,111 @@
     <t>Grabara</t>
   </si>
   <si>
+    <t>Recorde</t>
+  </si>
+  <si>
     <t>GOL</t>
   </si>
   <si>
     <t>Polônia</t>
   </si>
   <si>
+    <t>Detentor</t>
+  </si>
+  <si>
     <t>Elenco inicial</t>
   </si>
   <si>
+    <t>Quando</t>
+  </si>
+  <si>
     <t>Emprestado</t>
   </si>
   <si>
+    <t>Observacao</t>
+  </si>
+  <si>
     <t>Wellenreuther</t>
   </si>
   <si>
+    <t>Confirmado</t>
+  </si>
+  <si>
     <t>Alemanha</t>
   </si>
   <si>
+    <t>seq_vitorias</t>
+  </si>
+  <si>
+    <t>Maior sequência de vitórias</t>
+  </si>
+  <si>
     <t>Pervan</t>
   </si>
   <si>
+    <t>Bundesliga 2008/09</t>
+  </si>
+  <si>
     <t>Áustria</t>
   </si>
   <si>
+    <t>Sequência da campanha do título alemão</t>
+  </si>
+  <si>
     <t>Zieliński</t>
   </si>
   <si>
     <t>Wahl</t>
   </si>
   <si>
+    <t>SIM</t>
+  </si>
+  <si>
     <t>ZAG</t>
   </si>
   <si>
+    <t>maior_goleada</t>
+  </si>
+  <si>
+    <t>Maior goleada (saldo de gols)</t>
+  </si>
+  <si>
     <t>Adjetey</t>
   </si>
   <si>
+    <t>9 × 0 SV Hemelingen</t>
+  </si>
+  <si>
+    <t>16/08/2025 · DFB-Pokal, 1ª fase</t>
+  </si>
+  <si>
     <t>Gana</t>
   </si>
   <si>
+    <t>Recorde do clube na competição, confirmado pelo Wolfsburg</t>
+  </si>
+  <si>
     <t>Cleiton</t>
   </si>
   <si>
+    <t>gols_temporada</t>
+  </si>
+  <si>
     <t>Brasil</t>
   </si>
   <si>
+    <t>Mais gols de um jogador numa temporada</t>
+  </si>
+  <si>
+    <t>Grafite</t>
+  </si>
+  <si>
     <t>Angély</t>
   </si>
   <si>
+    <t>Artilheiro da Bundesliga na temporada do título</t>
+  </si>
+  <si>
     <t>França</t>
   </si>
   <si>
@@ -532,12 +589,54 @@
     <t>LD</t>
   </si>
   <si>
+    <t>assist_temporada</t>
+  </si>
+  <si>
+    <t>Mais assistências numa temporada</t>
+  </si>
+  <si>
     <t>Fischer</t>
   </si>
   <si>
+    <t>Kevin De Bruyne</t>
+  </si>
+  <si>
+    <t>Bundesliga 2014/15</t>
+  </si>
+  <si>
+    <t>Recorde da Bundesliga na época</t>
+  </si>
+  <si>
+    <t>artilheiro_historico</t>
+  </si>
+  <si>
+    <t>Maior artilheiro da história do clube</t>
+  </si>
+  <si>
+    <t>Edin Džeko</t>
+  </si>
+  <si>
+    <t>2007–2011</t>
+  </si>
+  <si>
+    <t>Gols na Bundesliga</t>
+  </si>
+  <si>
+    <t>titulos</t>
+  </si>
+  <si>
+    <t>Títulos de expressão</t>
+  </si>
+  <si>
+    <t>2009–2015</t>
+  </si>
+  <si>
     <t>Mæhle</t>
   </si>
   <si>
+    <t>Bundesliga 2008/09 · DFB-Pokal 2014/15 · Supercopa da Alemanha 2015</t>
+  </si>
+  <si>
     <t>Dinamarca</t>
   </si>
   <si>
@@ -571,276 +670,177 @@
     <t>Bélgica</t>
   </si>
   <si>
+    <t>Meta</t>
+  </si>
+  <si>
     <t>Hensel</t>
   </si>
   <si>
     <t>Dárdai</t>
   </si>
   <si>
+    <t>Status</t>
+  </si>
+  <si>
     <t>MEI</t>
   </si>
   <si>
     <t>Hungria</t>
   </si>
   <si>
-    <t>Recorde</t>
-  </si>
-  <si>
-    <t>Detentor</t>
-  </si>
-  <si>
-    <t>Quando</t>
-  </si>
-  <si>
-    <t>Observacao</t>
+    <t>Imagem</t>
+  </si>
+  <si>
+    <t>Atual</t>
+  </si>
+  <si>
+    <t>Alvo</t>
   </si>
   <si>
     <t>ATA</t>
   </si>
   <si>
-    <t>Meta</t>
-  </si>
-  <si>
-    <t>Confirmado</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>seq_vitorias</t>
-  </si>
-  <si>
-    <t>Maior sequência de vitórias</t>
-  </si>
-  <si>
-    <t>Imagem</t>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Subir como campeão</t>
   </si>
   <si>
     <t>Benedict</t>
   </si>
   <si>
-    <t>Atual</t>
-  </si>
-  <si>
     <t>PE</t>
   </si>
   <si>
-    <t>Alvo</t>
+    <t>Em andamento</t>
   </si>
   <si>
     <t>Amoura</t>
   </si>
   <si>
-    <t>Tipo</t>
-  </si>
-  <si>
-    <t>Bundesliga 2008/09</t>
+    <t>Conquistar o título da 2. Bundesliga e o acesso direto</t>
   </si>
   <si>
     <t>Argélia</t>
   </si>
   <si>
-    <t>Sequência da campanha do título alemão</t>
-  </si>
-  <si>
-    <t>Subir como campeão</t>
+    <t>subir-campeao.svg</t>
   </si>
   <si>
     <t>Hornby</t>
   </si>
   <si>
+    <t>Chegar às oitavas da DFB-Pokal</t>
+  </si>
+  <si>
     <t>Escócia</t>
   </si>
   <si>
-    <t>SIM</t>
-  </si>
-  <si>
-    <t>Em andamento</t>
-  </si>
-  <si>
-    <t>maior_goleada</t>
+    <t>Falhou</t>
   </si>
   <si>
     <t>Glatzel</t>
   </si>
   <si>
-    <t>Maior goleada (saldo de gols)</t>
-  </si>
-  <si>
-    <t>Conquistar o título da 2. Bundesliga e o acesso direto</t>
-  </si>
-  <si>
-    <t>9 × 0 SV Hemelingen</t>
-  </si>
-  <si>
-    <t>subir-campeao.svg</t>
-  </si>
-  <si>
-    <t>16/08/2025 · DFB-Pokal, 1ª fase</t>
-  </si>
-  <si>
-    <t>Recorde do clube na competição, confirmado pelo Wolfsburg</t>
-  </si>
-  <si>
-    <t>Chegar às oitavas da DFB-Pokal</t>
-  </si>
-  <si>
-    <t>Falhou</t>
+    <t>Eliminados pelo Freiburg na 2ª fase</t>
+  </si>
+  <si>
+    <t>oitavas-pokal.svg</t>
+  </si>
+  <si>
+    <t>Encontrar um novo D'Alessandro</t>
   </si>
   <si>
     <t>Japão</t>
   </si>
   <si>
-    <t>gols_temporada</t>
-  </si>
-  <si>
-    <t>Eliminados pelo Freiburg na 2ª fase</t>
-  </si>
-  <si>
-    <t>Mais gols de um jogador numa temporada</t>
-  </si>
-  <si>
-    <t>oitavas-pokal.svg</t>
-  </si>
-  <si>
     <t>Besio</t>
   </si>
   <si>
-    <t>Grafite</t>
-  </si>
-  <si>
-    <t>Encontrar um novo D'Alessandro</t>
-  </si>
-  <si>
-    <t>Artilheiro da Bundesliga na temporada do título</t>
+    <t>MEI argentino, canhoto, de 15 a 23 anos</t>
+  </si>
+  <si>
+    <t>novo-dalessandro.svg</t>
   </si>
   <si>
     <t>Suíça</t>
   </si>
   <si>
-    <t>MEI argentino, canhoto, de 15 a 23 anos</t>
-  </si>
-  <si>
-    <t>novo-dalessandro.svg</t>
-  </si>
-  <si>
-    <t>assist_temporada</t>
-  </si>
-  <si>
-    <t>Mais assistências numa temporada</t>
-  </si>
-  <si>
     <t>Scouting Sul-Americano</t>
   </si>
   <si>
-    <t>Kevin De Bruyne</t>
+    <t>Ter no elenco no mínimo 5 jogadores sul-americanos</t>
+  </si>
+  <si>
+    <t>scouting-sulamericano.svg</t>
   </si>
   <si>
     <t>Base</t>
   </si>
   <si>
-    <t>Bundesliga 2014/15</t>
-  </si>
-  <si>
-    <t>Ter no elenco no mínimo 5 jogadores sul-americanos</t>
-  </si>
-  <si>
-    <t>Recorde da Bundesliga na época</t>
-  </si>
-  <si>
-    <t>scouting-sulamericano.svg</t>
+    <t>sulamericanos</t>
   </si>
   <si>
     <t>Emiliano Martínez</t>
   </si>
   <si>
-    <t>artilheiro_historico</t>
-  </si>
-  <si>
-    <t>Maior artilheiro da história do clube</t>
-  </si>
-  <si>
-    <t>sulamericanos</t>
+    <t>Academia do Wolfsburg</t>
   </si>
   <si>
     <t>Uruguai</t>
   </si>
   <si>
+    <t>Categorias de base na Alemanha e na Argentina</t>
+  </si>
+  <si>
     <t>Reforço</t>
   </si>
   <si>
-    <t>Edin Džeko</t>
-  </si>
-  <si>
-    <t>Academia do Wolfsburg</t>
-  </si>
-  <si>
-    <t>2007–2011</t>
-  </si>
-  <si>
-    <t>Gols na Bundesliga</t>
+    <t>academia.svg</t>
   </si>
   <si>
     <t>Till Neininger</t>
   </si>
   <si>
-    <t>Categorias de base na Alemanha e na Argentina</t>
-  </si>
-  <si>
-    <t>academia.svg</t>
-  </si>
-  <si>
-    <t>titulos</t>
-  </si>
-  <si>
-    <t>Títulos de expressão</t>
-  </si>
-  <si>
     <t>Regras de contratação por janela</t>
   </si>
   <si>
-    <t>2009–2015</t>
+    <t>Vendeu € 10 mi: pode gastar até € 5 mi; Vendeu € 20 mi: até € 8 mi; Vendeu € 30 mi: até € 12 mi; Vendeu € 40 mi: até € 15 mi; Vendeu € 50 mi: até € 20 mi; Vendeu € 60 mi: até € 25 mi; Acima de € 60 mi: até 50% do valor das vendas</t>
+  </si>
+  <si>
+    <t>regras-transferencias.svg</t>
+  </si>
+  <si>
+    <t>Regra</t>
   </si>
   <si>
     <t>Andreas Skov Olsen</t>
   </si>
   <si>
-    <t>Bundesliga 2008/09 · DFB-Pokal 2014/15 · Supercopa da Alemanha 2015</t>
-  </si>
-  <si>
-    <t>Vendeu € 10 mi: pode gastar até € 5 mi; Vendeu € 20 mi: até € 8 mi; Vendeu € 30 mi: até € 12 mi; Vendeu € 40 mi: até € 15 mi; Vendeu € 50 mi: até € 20 mi; Vendeu € 60 mi: até € 25 mi; Acima de € 60 mi: até 50% do valor das vendas</t>
+    <t>Estilo de jogo</t>
+  </si>
+  <si>
+    <t>Inspirado no Internacional campeão da Sul-Americana 2008, no tradicional 4-3-1-2</t>
+  </si>
+  <si>
+    <t>estilo-de-jogo.svg</t>
+  </si>
+  <si>
+    <t>Regras de saída de jogadores</t>
   </si>
   <si>
     <t>B. Tomiak</t>
   </si>
   <si>
-    <t>regras-transferencias.svg</t>
-  </si>
-  <si>
-    <t>Regra</t>
-  </si>
-  <si>
-    <t>Estilo de jogo</t>
-  </si>
-  <si>
-    <t>Inspirado no Internacional campeão da Sul-Americana 2008, no tradicional 4-3-1-2</t>
-  </si>
-  <si>
-    <t>estilo-de-jogo.svg</t>
+    <t>Só podemos recusar propostas de compra se estivermos em 1º ou 2º lugar na Bundesliga</t>
+  </si>
+  <si>
+    <t>regras-saida.svg</t>
   </si>
   <si>
     <t>https://cdn.sofifa.net/players/262/119/26_120.png</t>
   </si>
   <si>
-    <t>Regras de saída de jogadores</t>
-  </si>
-  <si>
-    <t>Só podemos recusar propostas de compra se estivermos em 1º ou 2º lugar na Bundesliga</t>
-  </si>
-  <si>
-    <t>regras-saida.svg</t>
-  </si>
-  <si>
     <t>F. Kunze</t>
   </si>
   <si>
@@ -871,12 +871,27 @@
     <t>Eintracht-Stadion</t>
   </si>
   <si>
+    <t>Beşiktaş</t>
+  </si>
+  <si>
+    <t>Tigres</t>
+  </si>
+  <si>
+    <t>Selangor FA</t>
+  </si>
+  <si>
+    <t>Independiente Rivadavia</t>
+  </si>
+  <si>
+    <t>RW Essen</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/pt/c/c0/Rot-Weiss_Essen.png?utm_source=pt.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled&amp;_=20111219190251</t>
+  </si>
+  <si>
     <t>Saída</t>
   </si>
   <si>
-    <t>Beşiktaş</t>
-  </si>
-  <si>
     <t>Eriksen</t>
   </si>
   <si>
@@ -886,18 +901,6 @@
     <t>Problemas cardíacos</t>
   </si>
   <si>
-    <t>Tigres</t>
-  </si>
-  <si>
-    <t>Selangor FA</t>
-  </si>
-  <si>
-    <t>Independiente Rivadavia</t>
-  </si>
-  <si>
-    <t>https://pt.wikipedia.org/wiki/Ficheiro:Escudo_del_Club_Independiente_Rivadavia.svg</t>
-  </si>
-  <si>
     <t>Sem Clube</t>
   </si>
   <si>
@@ -914,15 +917,6 @@
   </si>
   <si>
     <t>Sai na temporada 27/28</t>
-  </si>
-  <si>
-    <t>2023/27</t>
-  </si>
-  <si>
-    <t>RW Essen</t>
-  </si>
-  <si>
-    <t>https://pt.wikipedia.org/wiki/Ficheiro:Rot-Weiss_Essen.png</t>
   </si>
 </sst>
 </file>
@@ -947,6 +941,12 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="10.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -955,12 +955,6 @@
       <b/>
       <sz val="11.0"/>
       <color rgb="FF2E7D32"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10.0"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -977,14 +971,14 @@
       <color rgb="FF0000FF"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
+      <u/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -1020,13 +1014,13 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -1037,7 +1031,7 @@
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1046,17 +1040,17 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1325,120 +1319,120 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2"/>
+      <c r="A2" s="3"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>1</v>
+      <c r="A3" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
+      <c r="A4" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
+      <c r="A5" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
+      <c r="A6" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2"/>
+      <c r="A7" s="3"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>5</v>
+      <c r="A8" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
+      <c r="A9" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>7</v>
+      <c r="A10" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>8</v>
+      <c r="A11" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>9</v>
+      <c r="A12" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>10</v>
+      <c r="A13" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>11</v>
+      <c r="A14" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>12</v>
+      <c r="A15" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>14</v>
+      <c r="A16" s="3" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>15</v>
+      <c r="A17" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2"/>
+      <c r="A18" s="3"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>16</v>
+      <c r="A19" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>17</v>
+      <c r="A20" s="3" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="2" t="s">
-        <v>18</v>
+      <c r="A21" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="2" t="s">
-        <v>19</v>
+      <c r="A22" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="2" t="s">
-        <v>22</v>
+      <c r="A23" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="2" t="s">
-        <v>23</v>
+      <c r="A24" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="2"/>
+      <c r="A25" s="3"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="2" t="s">
-        <v>25</v>
+      <c r="A26" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1"/>
@@ -2437,14 +2431,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>187</v>
+      <c r="A1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -3460,7 +3454,7 @@
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>278</v>
@@ -3471,45 +3465,42 @@
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="B3" s="14"/>
+        <v>280</v>
+      </c>
+      <c r="B3" s="13"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="B4" s="15"/>
+        <v>281</v>
+      </c>
+      <c r="B4" s="14"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="B5" s="15"/>
+        <v>282</v>
+      </c>
+      <c r="B5" s="14"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>288</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="B6" s="14"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="B2"/>
-    <hyperlink r:id="rId2" ref="B6"/>
-    <hyperlink r:id="rId3" ref="B7"/>
+    <hyperlink r:id="rId2" ref="B7"/>
   </hyperlinks>
-  <drawing r:id="rId4"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -3526,66 +3517,66 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="D1" s="13" t="s">
+      <c r="A1" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="D1" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="F1" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>187</v>
+      <c r="F1" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B2" s="6">
         <v>1.0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="F2" s="6">
         <v>0.0</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B3" s="6">
         <v>6.0</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>280</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>281</v>
       </c>
       <c r="F3" s="6">
         <v>1.9E7</v>
@@ -3593,19 +3584,19 @@
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B4" s="6">
         <v>6.0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="F4" s="6">
         <v>7000000.0</v>
@@ -3613,7 +3604,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B5" s="6">
         <v>6.0</v>
@@ -3622,107 +3613,107 @@
         <v>143</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F5" s="6">
         <v>0.0</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B6" s="6">
         <v>6.0</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F6" s="6">
         <v>0.0</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B7" s="6">
         <v>6.0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B8" s="6">
         <v>6.0</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>180</v>
+        <v>214</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B9" s="6">
         <v>7.0</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F9" s="6">
         <v>8500000.0</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B10" s="6">
         <v>7.0</v>
@@ -3731,7 +3722,7 @@
         <v>143</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>81</v>
@@ -3742,7 +3733,7 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B11" s="6">
         <v>7.0</v>
@@ -3754,7 +3745,7 @@
         <v>270</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F11" s="6">
         <v>2300000.0</v>
@@ -3762,7 +3753,7 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B12" s="6">
         <v>7.0</v>
@@ -3774,7 +3765,7 @@
         <v>271</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F12" s="6">
         <v>2000000.0</v>
@@ -3782,7 +3773,7 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>295</v>
+        <v>25</v>
       </c>
       <c r="B13" s="6">
         <v>7.0</v>
@@ -3794,7 +3785,7 @@
         <v>273</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="F13" s="6">
         <v>560000.0</v>
@@ -3819,154 +3810,154 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>21</v>
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>31</v>
+        <v>20</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B11" s="5">
         <v>2.0</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>67</v>
+      <c r="C11" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B12" s="5">
         <v>3.0</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>69</v>
+      <c r="C12" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B13" s="5">
         <v>16.0</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>73</v>
+      <c r="C13" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B14" s="5">
         <v>17.0</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>76</v>
+      <c r="C14" s="3" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -3976,7 +3967,7 @@
       <c r="B15" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>80</v>
       </c>
     </row>
@@ -4985,23 +4976,23 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>45</v>
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="2">
@@ -5009,19 +5000,19 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="D2" s="7">
         <v>46302.0</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3">
@@ -5029,19 +5020,19 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D3" s="7">
         <v>46304.0</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4">
@@ -5049,19 +5040,19 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D4" s="7">
         <v>46308.0</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -5069,19 +5060,19 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D5" s="7">
         <v>46311.0</v>
       </c>
       <c r="E5" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>107</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="6">
@@ -5089,19 +5080,19 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D6" s="7">
         <v>46315.0</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7">
@@ -5109,19 +5100,19 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D7" s="11">
         <v>46318.0</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8">
@@ -5129,19 +5120,19 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D8" s="11">
         <v>46322.0</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -6161,32 +6152,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>57</v>
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="2">
@@ -6197,19 +6188,19 @@
         <v>1.0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E2" s="6">
         <v>1.0</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H2" s="6">
         <v>4.0</v>
@@ -6226,19 +6217,19 @@
         <v>1.0</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E3" s="6">
         <v>1.0</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H3" s="6">
         <v>4.0</v>
@@ -6255,10 +6246,10 @@
         <v>1.0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E4" s="6">
         <v>2.0</v>
@@ -6284,10 +6275,10 @@
         <v>1.0</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E5" s="6">
         <v>3.0</v>
@@ -6313,19 +6304,19 @@
         <v>2.0</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E6" s="6">
         <v>4.0</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H6" s="6">
         <v>2.0</v>
@@ -6342,16 +6333,16 @@
         <v>2.0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E7" s="6">
         <v>5.0</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>82</v>
@@ -6371,19 +6362,19 @@
         <v>2.0</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E8" s="6">
         <v>6.0</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H8" s="6">
         <v>1.0</v>
@@ -6400,10 +6391,10 @@
         <v>2.0</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E9" s="6">
         <v>7.0</v>
@@ -6429,10 +6420,10 @@
         <v>3.0</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E10" s="6">
         <v>8.0</v>
@@ -6441,7 +6432,7 @@
         <v>91</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H10" s="6">
         <v>4.0</v>
@@ -6458,10 +6449,10 @@
         <v>3.0</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E11" s="6">
         <v>9.0</v>
@@ -6487,19 +6478,19 @@
         <v>3.0</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E12" s="6">
         <v>2.0</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H12" s="6">
         <v>0.0</v>
@@ -6516,19 +6507,19 @@
         <v>3.0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E13" s="6">
         <v>10.0</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H13" s="6">
         <v>5.0</v>
@@ -6545,16 +6536,16 @@
         <v>4.0</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E14" s="6">
         <v>11.0</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>82</v>
@@ -6574,10 +6565,10 @@
         <v>4.0</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E15" s="6">
         <v>12.0</v>
@@ -6586,7 +6577,7 @@
         <v>99</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H15" s="6">
         <v>1.0</v>
@@ -6603,16 +6594,16 @@
         <v>4.0</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E16" s="6">
         <v>13.0</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>82</v>
@@ -6632,19 +6623,19 @@
         <v>5.0</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E17" s="6">
         <v>14.0</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H17" s="6">
         <v>1.0</v>
@@ -6661,16 +6652,16 @@
         <v>5.0</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E18" s="6">
         <v>15.0</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>82</v>
@@ -6690,19 +6681,19 @@
         <v>5.0</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E19" s="6">
         <v>16.0</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H19" s="6">
         <v>2.0</v>
@@ -6719,16 +6710,16 @@
         <v>6.0</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E20" s="6">
         <v>17.0</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>82</v>
@@ -6748,16 +6739,16 @@
         <v>6.0</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E21" s="6">
         <v>18.0</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>82</v>
@@ -6777,10 +6768,10 @@
         <v>6.0</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E22" s="6">
         <v>19.0</v>
@@ -6789,7 +6780,7 @@
         <v>81</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H22" s="6">
         <v>2.0</v>
@@ -6806,10 +6797,10 @@
         <v>7.0</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E23" s="6">
         <v>20.0</v>
@@ -6818,7 +6809,7 @@
         <v>83</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H23" s="6">
         <v>0.0</v>
@@ -6835,16 +6826,16 @@
         <v>7.0</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E24" s="6">
         <v>21.0</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>82</v>
@@ -6864,16 +6855,16 @@
         <v>7.0</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E25" s="6">
         <v>22.0</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>82</v>
@@ -6893,16 +6884,16 @@
         <v>7.0</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E26" s="6">
         <v>23.0</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>82</v>
@@ -10840,17 +10831,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>110</v>
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="2">
@@ -10861,10 +10852,10 @@
         <v>33.0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3">
@@ -10875,10 +10866,10 @@
         <v>38.0</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4">
@@ -10889,10 +10880,10 @@
         <v>50.0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5">
@@ -10903,10 +10894,10 @@
         <v>57.0</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="6">
@@ -10917,10 +10908,10 @@
         <v>17.0</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7">
@@ -10931,10 +10922,10 @@
         <v>42.0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8">
@@ -10945,7 +10936,7 @@
         <v>59.0</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9">
@@ -10956,10 +10947,10 @@
         <v>86.0</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10">
@@ -10970,10 +10961,10 @@
         <v>28.0</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11">
@@ -10984,7 +10975,7 @@
         <v>53.0</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12">
@@ -10995,10 +10986,10 @@
         <v>45.0</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -11009,10 +11000,10 @@
         <v>82.0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -11023,10 +11014,10 @@
         <v>8.0</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15">
@@ -11037,10 +11028,10 @@
         <v>80.0</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -11051,10 +11042,10 @@
         <v>75.0</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17">
@@ -11065,10 +11056,10 @@
         <v>73.0</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18">
@@ -11079,10 +11070,10 @@
         <v>28.0</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19">
@@ -11093,10 +11084,10 @@
         <v>35.0</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20">
@@ -11107,10 +11098,10 @@
         <v>40.0</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -11121,10 +11112,10 @@
         <v>88.0</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -11135,10 +11126,10 @@
         <v>28.0</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -11149,10 +11140,10 @@
         <v>27.0</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -11163,10 +11154,10 @@
         <v>37.0</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -11177,10 +11168,10 @@
         <v>39.0</v>
       </c>
       <c r="C25" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -11191,10 +11182,10 @@
         <v>56.0</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
@@ -11205,10 +11196,10 @@
         <v>69.0</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -11219,10 +11210,10 @@
         <v>4.0</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -11233,10 +11224,10 @@
         <v>7.0</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -11247,10 +11238,10 @@
         <v>39.0</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
@@ -11261,10 +11252,10 @@
         <v>59.0</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
@@ -11275,10 +11266,10 @@
         <v>82.0</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
@@ -11289,10 +11280,10 @@
         <v>47.0</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
@@ -11303,10 +11294,10 @@
         <v>3.0</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
@@ -11317,10 +11308,10 @@
         <v>63.0</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
@@ -11331,10 +11322,10 @@
         <v>74.0</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
@@ -11345,10 +11336,10 @@
         <v>82.0</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
@@ -11359,10 +11350,10 @@
         <v>83.0</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
@@ -11373,10 +11364,10 @@
         <v>51.0</v>
       </c>
       <c r="C39" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D39" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
@@ -11387,10 +11378,10 @@
         <v>71.0</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
@@ -11401,10 +11392,10 @@
         <v>20.0</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
@@ -11415,10 +11406,10 @@
         <v>84.0</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
@@ -11429,10 +11420,10 @@
         <v>41.0</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
@@ -11443,10 +11434,10 @@
         <v>49.0</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
@@ -11457,10 +11448,10 @@
         <v>55.0</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1"/>
@@ -12441,32 +12432,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="4" t="s">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="H1" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="I1" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="2">
@@ -12477,7 +12468,7 @@
         <v>1.0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D2" s="6">
         <v>23.0</v>
@@ -12506,7 +12497,7 @@
         <v>2.0</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D3" s="6">
         <v>23.0</v>
@@ -12535,7 +12526,7 @@
         <v>3.0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D4" s="6">
         <v>23.0</v>
@@ -12593,7 +12584,7 @@
         <v>5.0</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D6" s="6">
         <v>23.0</v>
@@ -12622,7 +12613,7 @@
         <v>6.0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D7" s="6">
         <v>23.0</v>
@@ -13655,7 +13646,7 @@
         <v>139</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C1" s="12" t="s">
         <v>140</v>
@@ -13684,439 +13675,439 @@
         <v>147</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>152</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>153</v>
-      </c>
       <c r="E6" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>170</v>
+        <v>203</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>171</v>
+        <v>204</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
-        <v>172</v>
+        <v>205</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>171</v>
+        <v>204</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>176</v>
+        <v>209</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>180</v>
+        <v>214</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>183</v>
+        <v>218</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="6" t="s">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>197</v>
+        <v>226</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="6" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="6" t="s">
-        <v>205</v>
+        <v>232</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>210</v>
+        <v>236</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="6" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="F32" s="6">
         <v>3.0</v>
@@ -14124,16 +14115,16 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="6" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F33" s="6">
         <v>6.0</v>
@@ -14141,56 +14132,56 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="6" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B34" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D34" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>153</v>
-      </c>
       <c r="E34" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="6" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="6" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B36" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D36" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>153</v>
-      </c>
       <c r="E36" s="6" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F36" s="6">
         <v>7.0</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
@@ -14198,13 +14189,13 @@
         <v>270</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F37" s="6">
         <v>7.0</v>
@@ -14215,13 +14206,13 @@
         <v>271</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>272</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F38" s="6">
         <v>7.0</v>
@@ -14232,13 +14223,13 @@
         <v>273</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>274</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F39" s="6">
         <v>7.0</v>
@@ -15550,167 +15541,167 @@
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>184</v>
+        <v>148</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>185</v>
+        <v>151</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>186</v>
+        <v>153</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>193</v>
+        <v>160</v>
       </c>
       <c r="C2" s="6">
         <v>10.0</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>201</v>
+        <v>162</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>209</v>
+        <v>169</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="C3" s="6">
         <v>9.0</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>213</v>
+        <v>172</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>215</v>
+        <v>173</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>220</v>
+        <v>177</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>222</v>
+        <v>179</v>
       </c>
       <c r="C4" s="6">
         <v>28.0</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>225</v>
+        <v>180</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>201</v>
+        <v>162</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>227</v>
+        <v>182</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>231</v>
+        <v>186</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>232</v>
+        <v>187</v>
       </c>
       <c r="C5" s="6">
         <v>20.0</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>234</v>
+        <v>189</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>236</v>
+        <v>190</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>238</v>
+        <v>191</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>241</v>
+        <v>192</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>242</v>
+        <v>193</v>
       </c>
       <c r="C6" s="6">
         <v>66.0</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>246</v>
+        <v>194</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>248</v>
+        <v>195</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>249</v>
+        <v>196</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>253</v>
+        <v>197</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>254</v>
+        <v>198</v>
       </c>
       <c r="C7" s="6">
         <v>3.0</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>256</v>
+        <v>199</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>258</v>
+        <v>201</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8">
-      <c r="F8" s="2"/>
+      <c r="F8" s="3"/>
       <c r="G8" s="5"/>
     </row>
     <row r="9">
@@ -16922,96 +16913,96 @@
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="E5" s="6">
         <v>2.0</v>
@@ -17020,72 +17011,72 @@
         <v>5.0</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>261</v>
-      </c>
       <c r="H7" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>265</v>
-      </c>
       <c r="H8" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>269</v>
-      </c>
       <c r="H9" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">

--- a/dados/series/fc27-tango-lobos/dados.xlsx
+++ b/dados/series/fc27-tango-lobos/dados.xlsx
@@ -27,147 +27,165 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="298">
   <si>
     <t>Histórias em Campo — planilha do portal</t>
   </si>
   <si>
+    <t>Episodio</t>
+  </si>
+  <si>
     <t>Chave</t>
   </si>
   <si>
-    <t>Episodio</t>
+    <t>COMO USAR</t>
+  </si>
+  <si>
+    <t>1. Cada aba alimenta uma parte do site. Não renomeie as abas nem os títulos das colunas (linha 1).</t>
+  </si>
+  <si>
+    <t>Temporada</t>
+  </si>
+  <si>
+    <t>2. Preencha a partir da linha 2. Uma linha = um registro. Listas suspensas ajudam nas colunas Local, Competicao, Posicao, Status e Confirmado.</t>
   </si>
   <si>
     <t>Valor</t>
   </si>
   <si>
+    <t>Titulo</t>
+  </si>
+  <si>
+    <t>3. Depois de salvar, o site atualiza sozinho (ou envie o arquivo para a pasta 'dados' do site no GitHub com o nome dados.xlsx).</t>
+  </si>
+  <si>
+    <t>Jogo</t>
+  </si>
+  <si>
     <t>Descricao</t>
   </si>
   <si>
-    <t>COMO USAR</t>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>ABAS</t>
   </si>
   <si>
     <t>nome_portal</t>
   </si>
   <si>
-    <t>Temporada</t>
-  </si>
-  <si>
-    <t>1. Cada aba alimenta uma parte do site. Não renomeie as abas nem os títulos das colunas (linha 1).</t>
+    <t>Link YouTube</t>
+  </si>
+  <si>
+    <t>Clube — configurações gerais: nome do portal, cores, temporada atual e zonas da tabela (acesso, playoff, rebaixamento).</t>
+  </si>
+  <si>
+    <t>Resumo</t>
+  </si>
+  <si>
+    <t>Episodios — um episódio por linha: número, temporada e um resumo curto. Titulo, Data e Link YouTube podem ficar em branco: o site busca sozinho no canal (vídeos com 'EP 01', 'EP 02'... no título). Se preencher, o que estiver na planilha tem prioridade. A INTRO entra sozinha pelo YouTube.</t>
+  </si>
+  <si>
+    <t>Competicao</t>
   </si>
   <si>
     <t>Histórias em Campo</t>
   </si>
   <si>
-    <t>Titulo</t>
-  </si>
-  <si>
-    <t>2. Preencha a partir da linha 2. Uma linha = um registro. Listas suspensas ajudam nas colunas Local, Competicao, Posicao, Status e Confirmado.</t>
-  </si>
-  <si>
-    <t>Jogo</t>
-  </si>
-  <si>
-    <t>3. Depois de salvar, o site atualiza sozinho (ou envie o arquivo para a pasta 'dados' do site no GitHub com o nome dados.xlsx).</t>
+    <t>2026/27</t>
+  </si>
+  <si>
+    <t>Jogos — um jogo por linha, em ordem cronológica. A coluna Jogo é um número sequencial (1, 2, 3...) e é ela que liga os gols ao jogo. O resultado (V/E/D) é calculado pelo site.</t>
+  </si>
+  <si>
+    <t>Rodada</t>
   </si>
   <si>
     <t>Nome exibido no topo do site</t>
   </si>
   <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>Link YouTube</t>
-  </si>
-  <si>
-    <t>ABAS</t>
+    <t>Adversario</t>
+  </si>
+  <si>
+    <t>Gols — um gol do clube por linha: número do Jogo, Minuto, Autor e Assistencia (deixe vazio se não houve assistência). Minuto é só o número (ex.: 23); nos acréscimos use 45+2 ou 90+3. Para gol contra do adversário, escreva 'Gol contra' em Autor.</t>
+  </si>
+  <si>
+    <t>CHEGOU o MODO CARREIRA mais REALISTA do YOUTUBE | FC 27 Modo Carreira Realista Wolfsburg| EP 01</t>
+  </si>
+  <si>
+    <t>Local</t>
   </si>
   <si>
     <t>clube</t>
   </si>
   <si>
-    <t>Resumo</t>
+    <t>Classificacao — a tabela completa ao final de cada episódio (todas as 18 equipes, uma linha cada). Pontos e saldo de gols são calculados pelo site.</t>
   </si>
   <si>
     <t>VfL Wolfsburg</t>
   </si>
   <si>
-    <t>Clube — configurações gerais: nome do portal, cores, temporada atual e zonas da tabela (acesso, playoff, rebaixamento).</t>
+    <t>Gols Pro</t>
   </si>
   <si>
     <t>Nome do clube exatamente como aparece na aba Classificacao</t>
   </si>
   <si>
+    <t>Elenco — jogadores do elenco com posição e número. Use exatamente os mesmos nomes da aba Gols.</t>
+  </si>
+  <si>
+    <t>Gols Contra</t>
+  </si>
+  <si>
     <t>canal</t>
   </si>
   <si>
-    <t>Episodios — um episódio por linha: número, temporada e um resumo curto. Titulo, Data e Link YouTube podem ficar em branco: o site busca sozinho no canal (vídeos com 'EP 01', 'EP 02'... no título). Se preencher, o que estiver na planilha tem prioridade. A INTRO entra sozinha pelo YouTube.</t>
-  </si>
-  <si>
-    <t>2026/27</t>
-  </si>
-  <si>
-    <t>Competicao</t>
-  </si>
-  <si>
     <t>@gabbiDOMFC</t>
   </si>
   <si>
+    <t>Recordes — recordes reais do clube até o início da série (temporada 2026/27). NÃO altere a coluna Chave. Edite Valor, Detentor e Quando. Confirmado = SIM tira o aviso 'a confirmar' do site.</t>
+  </si>
+  <si>
     <t>Nome do canal</t>
   </si>
   <si>
-    <t>Rodada</t>
-  </si>
-  <si>
-    <t>CHEGOU o MODO CARREIRA mais REALISTA do YOUTUBE | FC 27 Modo Carreira Realista Wolfsburg| EP 01</t>
-  </si>
-  <si>
-    <t>Jogos — um jogo por linha, em ordem cronológica. A coluna Jogo é um número sequencial (1, 2, 3...) e é ela que liga os gols ao jogo. O resultado (V/E/D) é calculado pelo site.</t>
+    <t>Metas — objetivos da carreira, com Status: Em andamento, Concluída ou Falhou.</t>
   </si>
   <si>
     <t>link_canal</t>
   </si>
   <si>
-    <t>Adversario</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/@gabbiDOMFC</t>
   </si>
   <si>
-    <t>Gols — um gol do clube por linha: número do Jogo, Minuto, Autor e Assistencia (deixe vazio se não houve assistência). Minuto é só o número (ex.: 23); nos acréscimos use 45+2 ou 90+3. Para gol contra do adversário, escreva 'Gol contra' em Autor.</t>
+    <t>26/27</t>
   </si>
   <si>
     <t>Link do canal no YouTube</t>
   </si>
   <si>
-    <t>Local</t>
-  </si>
-  <si>
-    <t>Classificacao — a tabela completa ao final de cada episódio (todas as 18 equipes, uma linha cada). Pontos e saldo de gols são calculados pelo site.</t>
+    <t>https://www.youtube.com/watch?v=AMmtV3qhNEI</t>
+  </si>
+  <si>
+    <t>Titulos — títulos conquistados na carreira (uma linha por título).</t>
   </si>
   <si>
     <t>temporada_atual</t>
   </si>
   <si>
-    <t>Gols Pro</t>
-  </si>
-  <si>
-    <t>Elenco — jogadores do elenco com posição e número. Use exatamente os mesmos nomes da aba Gols.</t>
-  </si>
-  <si>
-    <t>Gols Contra</t>
-  </si>
-  <si>
     <t>Temporada mostrada na página inicial</t>
   </si>
   <si>
-    <t>Recordes — recordes reais do clube até o início da série (temporada 2026/27). NÃO altere a coluna Chave. Edite Valor, Detentor e Quando. Confirmado = SIM tira o aviso 'a confirmar' do site.</t>
+    <t>EXEMPLOS DE PREENCHIMENTO</t>
   </si>
   <si>
     <t>competicao_liga</t>
   </si>
   <si>
-    <t>Metas — objetivos da carreira, com Status: Em andamento, Concluída ou Falhou.</t>
+    <t>DFB-Pokal</t>
+  </si>
+  <si>
+    <t>Episodios:  1 | 2026/27 | (vazio) | (vazio) | (vazio) | Estreia na 2. Bundesliga com vitória em casa.</t>
   </si>
   <si>
     <t>2. Bundesliga</t>
@@ -176,13 +194,10 @@
     <t>Nome da liga, igual ao usado na aba Jogos</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=AMmtV3qhNEI</t>
-  </si>
-  <si>
-    <t>Titulos — títulos conquistados na carreira (uma linha por título).</t>
-  </si>
-  <si>
-    <t>26/27</t>
+    <t>1. FC Kaiserslautern</t>
+  </si>
+  <si>
+    <t>Jogos:  1 | 1 | 2026/27 | 2. Bundesliga | 1 | Hertha BSC | Casa | 2 | 0</t>
   </si>
   <si>
     <t>cor_primaria</t>
@@ -191,13 +206,16 @@
     <t>#65B32E</t>
   </si>
   <si>
-    <t>EXEMPLOS DE PREENCHIMENTO</t>
+    <t>Gols:  1 | 34 | Nome do Jogador | Nome de quem deu a assistência</t>
   </si>
   <si>
     <t>Cor principal do site (código hexadecimal)</t>
   </si>
   <si>
-    <t>Episodios:  1 | 2026/27 | (vazio) | (vazio) | (vazio) | Estreia na 2. Bundesliga com vitória em casa.</t>
+    <t>Casa</t>
+  </si>
+  <si>
+    <t>Classificacao:  1 | 1 | VfL Wolfsburg | 1 | 1 | 0 | 0 | 2 | 0   (Episodio | Posicao | Time | J | V | E | D | GP | GC)</t>
   </si>
   <si>
     <t>cor_secundaria</t>
@@ -206,51 +224,33 @@
     <t>#1E4D2B</t>
   </si>
   <si>
+    <t>Elenco:  Nome do Jogador | ATA | 9 | Alemanha</t>
+  </si>
+  <si>
     <t>Cor de apoio (fundo do topo)</t>
   </si>
   <si>
-    <t>Jogos:  1 | 1 | 2026/27 | 2. Bundesliga | 1 | Hertha BSC | Casa | 2 | 0</t>
-  </si>
-  <si>
     <t>escudo</t>
   </si>
   <si>
+    <t>ATENÇÃO: os recordes reais estão marcados como 'a confirmar'. Confira cada valor antes de divulgar e mude Confirmado para SIM.</t>
+  </si>
+  <si>
     <t>Nome do arquivo de imagem do escudo colocado na pasta do site (ex.: escudo.png). Vazio = monograma</t>
   </si>
   <si>
-    <t>Gols:  1 | 34 | Nome do Jogador | Nome de quem deu a assistência</t>
-  </si>
-  <si>
-    <t>DFB-Pokal</t>
-  </si>
-  <si>
     <t>zona_acesso</t>
   </si>
   <si>
-    <t>Classificacao:  1 | 1 | VfL Wolfsburg | 1 | 1 | 0 | 0 | 2 | 0   (Episodio | Posicao | Time | J | V | E | D | GP | GC)</t>
-  </si>
-  <si>
-    <t>1. FC Kaiserslautern</t>
-  </si>
-  <si>
     <t>Até esta posição: acesso direto</t>
   </si>
   <si>
-    <t>Elenco:  Nome do Jogador | ATA | 9 | Alemanha</t>
-  </si>
-  <si>
     <t>zona_playoff_acesso</t>
   </si>
   <si>
-    <t>Casa</t>
-  </si>
-  <si>
     <t>Posição do playoff de acesso</t>
   </si>
   <si>
-    <t>ATENÇÃO: os recordes reais estão marcados como 'a confirmar'. Confira cada valor antes de divulgar e mude Confirmado para SIM.</t>
-  </si>
-  <si>
     <t>zona_playoff_rebaixamento</t>
   </si>
   <si>
@@ -263,55 +263,58 @@
     <t>A partir desta posição: rebaixamento direto</t>
   </si>
   <si>
+    <t>Hannover 96</t>
+  </si>
+  <si>
     <t>dados_exemplo</t>
   </si>
   <si>
     <t>NAO</t>
   </si>
   <si>
+    <t>Fora</t>
+  </si>
+  <si>
     <t>SIM mostra um aviso de dados de exemplo no site</t>
   </si>
   <si>
-    <t>Hannover 96</t>
-  </si>
-  <si>
-    <t>Fora</t>
-  </si>
-  <si>
     <t>Karlsruher SC</t>
   </si>
   <si>
+    <t>Energie Cottbus</t>
+  </si>
+  <si>
+    <t>FC St. Pauli</t>
+  </si>
+  <si>
+    <t>SV Darmstadt 98</t>
+  </si>
+  <si>
     <t>Início eletrizante do modo carreira realista com o Wolfsburg agora no comando de um antigo conhecido: Andrés D'Alessandro. Um esboço de time já apresenta gratas surpresas para o decorrer da temporada.</t>
   </si>
   <si>
+    <t>1. FC Nürnberg</t>
+  </si>
+  <si>
     <t>SÓ TEM RETRANQUEIRO NA SEGUNDA DIVISÃO? | FC 27 Modo Carreira Realista Wolfsburg| EP 02</t>
   </si>
   <si>
-    <t>Energie Cottbus</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=eB3sg-pBc1k</t>
   </si>
   <si>
-    <t>FC St. Pauli</t>
-  </si>
-  <si>
-    <t>SV Darmstadt 98</t>
-  </si>
-  <si>
-    <t>1. FC Nürnberg</t>
-  </si>
-  <si>
     <t>Heidenheim 1846</t>
   </si>
   <si>
     <t>VfL Bochum</t>
   </si>
   <si>
+    <t>Sport-Club Freiburg</t>
+  </si>
+  <si>
     <t>D'Alessandro está com dificuldades de enfrentar clubes que acabam joganado de forma mais defensiva. Será que ele consegue encontrar uma solução para furar essas retrancas? Descubra neste episódio.</t>
   </si>
   <si>
-    <t>Sport-Club Freiburg</t>
+    <t>VfL Osnabrück</t>
   </si>
   <si>
     <t>TEMOS um CRISTIANO RONALDO JAPONÊS?! 🐐 | FC 27 Modo Carreira Realista Wolfsburg| EP 03</t>
@@ -320,43 +323,40 @@
     <t>https://www.youtube.com/watch?v=mJnFU4fK3lQ</t>
   </si>
   <si>
-    <t>VfL Osnabrück</t>
-  </si>
-  <si>
     <t>Hertha BSC</t>
   </si>
   <si>
     <t>Holstein Kiel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A sensação japonesa não se cansa de marcar. Será que estamos diante de um CR7 nipônico? </t>
   </si>
   <si>
     <t xml:space="preserve">Eintracht Braunschweig
 </t>
   </si>
   <si>
+    <t>1. FC Magdeburg</t>
+  </si>
+  <si>
+    <t>SpVgg Greuther Fürth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A sensação japonesa não se cansa de marcar. Será que estamos diante de um CR7 nipônico? </t>
+  </si>
+  <si>
     <t>O nível SUBIU! Tomamos um AMASSO? | FC 27 Modo Carreira Realista Wolfsburg| EP 04</t>
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=LW1zoO_I704</t>
   </si>
   <si>
-    <t>1. FC Magdeburg</t>
-  </si>
-  <si>
-    <t>SpVgg Greuther Fürth</t>
-  </si>
-  <si>
     <t>Arminia Bielefeld</t>
   </si>
   <si>
+    <t>Dynamo Dresden</t>
+  </si>
+  <si>
     <t>Os sliders chegaram com tudo, a dificuldade aumentou e nosso time sentiu na pele. Será o fim da boa fase?</t>
   </si>
   <si>
-    <t>Dynamo Dresden</t>
-  </si>
-  <si>
     <t>ELE está nos salvando do PIOR! | FC 27 Modo Carreira Realista Wolfsburg| EP 05</t>
   </si>
   <si>
@@ -370,21 +370,6 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=N_UrK97rWAQ</t>
-  </si>
-  <si>
-    <t>Minuto</t>
-  </si>
-  <si>
-    <t>Autor</t>
-  </si>
-  <si>
-    <t>Assistencia</t>
-  </si>
-  <si>
-    <t>Damar</t>
-  </si>
-  <si>
-    <t>Shiogai</t>
   </si>
   <si>
     <t>O Wolfsburg que vocês conheciam não existe mais. D'Alessandro colocou o cargo à disposição, o clube entrou em crise e só restou um caminho: uma reestruturação completa, dentro e fora de campo. E o primeiro passo pode vir do Uruguai…</t>
@@ -394,24 +379,46 @@
 </t>
   </si>
   <si>
+    <t>https://www.youtube.com/watch?v=lZ5DxuA-Jms&amp;t=1399s</t>
+  </si>
+  <si>
+    <t>Minuto</t>
+  </si>
+  <si>
+    <t>Autor</t>
+  </si>
+  <si>
+    <t>Assistencia</t>
+  </si>
+  <si>
+    <t>Damar</t>
+  </si>
+  <si>
+    <t>Shiogai</t>
+  </si>
+  <si>
     <t>Arnold</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=lZ5DxuA-Jms&amp;t=1399s</t>
-  </si>
-  <si>
     <t>Reese</t>
   </si>
   <si>
+    <t>Faltando poucas horas pro fim da janela, o Barcelona ligou. Eles queriam o nosso artilheiro. Entre 4 reforços chegando e uma decisão que pode mudar a temporada inteira, o novo Wolfsburg começa a tomar forma no nosso Modo Carreira Realista do FC 27.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O artilheiro SUMIU… e ELE assumiu a responsabilidade | FC 27 Modo Carreira Realista | EP 08
+</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=lRjz74Rfh6s&amp;t=1582s</t>
+  </si>
+  <si>
     <t>Bernhardsson</t>
   </si>
   <si>
     <t>Svanberg</t>
   </si>
   <si>
-    <t>Faltando poucas horas pro fim da janela, o Barcelona ligou. Eles queriam o nosso artilheiro. Entre 4 reforços chegando e uma decisão que pode mudar a temporada inteira, o novo Wolfsburg começa a tomar forma no nosso Modo Carreira Realista do FC 27.</t>
-  </si>
-  <si>
     <t>Posicao</t>
   </si>
   <si>
@@ -484,28 +491,31 @@
     <t>Polônia</t>
   </si>
   <si>
+    <t>Elenco inicial</t>
+  </si>
+  <si>
     <t>Detentor</t>
   </si>
   <si>
-    <t>Elenco inicial</t>
+    <t>Emprestado</t>
   </si>
   <si>
     <t>Quando</t>
   </si>
   <si>
-    <t>Emprestado</t>
+    <t>Wellenreuther</t>
   </si>
   <si>
     <t>Observacao</t>
   </si>
   <si>
-    <t>Wellenreuther</t>
+    <t>Alemanha</t>
   </si>
   <si>
     <t>Confirmado</t>
   </si>
   <si>
-    <t>Alemanha</t>
+    <t>Pervan</t>
   </si>
   <si>
     <t>seq_vitorias</t>
@@ -514,30 +524,27 @@
     <t>Maior sequência de vitórias</t>
   </si>
   <si>
-    <t>Pervan</t>
+    <t>Áustria</t>
   </si>
   <si>
     <t>Bundesliga 2008/09</t>
   </si>
   <si>
-    <t>Áustria</t>
+    <t>Zieliński</t>
   </si>
   <si>
     <t>Sequência da campanha do título alemão</t>
   </si>
   <si>
-    <t>Zieliński</t>
-  </si>
-  <si>
     <t>Wahl</t>
   </si>
   <si>
+    <t>ZAG</t>
+  </si>
+  <si>
     <t>SIM</t>
   </si>
   <si>
-    <t>ZAG</t>
-  </si>
-  <si>
     <t>maior_goleada</t>
   </si>
   <si>
@@ -583,36 +590,39 @@
     <t>França</t>
   </si>
   <si>
+    <t>assist_temporada</t>
+  </si>
+  <si>
     <t>Kumbedi</t>
   </si>
   <si>
+    <t>Mais assistências numa temporada</t>
+  </si>
+  <si>
     <t>LD</t>
   </si>
   <si>
-    <t>assist_temporada</t>
-  </si>
-  <si>
-    <t>Mais assistências numa temporada</t>
+    <t>Kevin De Bruyne</t>
+  </si>
+  <si>
+    <t>Bundesliga 2014/15</t>
+  </si>
+  <si>
+    <t>Recorde da Bundesliga na época</t>
   </si>
   <si>
     <t>Fischer</t>
   </si>
   <si>
-    <t>Kevin De Bruyne</t>
-  </si>
-  <si>
-    <t>Bundesliga 2014/15</t>
-  </si>
-  <si>
-    <t>Recorde da Bundesliga na época</t>
-  </si>
-  <si>
     <t>artilheiro_historico</t>
   </si>
   <si>
     <t>Maior artilheiro da história do clube</t>
   </si>
   <si>
+    <t>Mæhle</t>
+  </si>
+  <si>
     <t>Edin Džeko</t>
   </si>
   <si>
@@ -622,30 +632,27 @@
     <t>Gols na Bundesliga</t>
   </si>
   <si>
+    <t>Dinamarca</t>
+  </si>
+  <si>
+    <t>Zehnter</t>
+  </si>
+  <si>
     <t>titulos</t>
   </si>
   <si>
     <t>Títulos de expressão</t>
   </si>
   <si>
+    <t>LE</t>
+  </si>
+  <si>
     <t>2009–2015</t>
   </si>
   <si>
-    <t>Mæhle</t>
-  </si>
-  <si>
     <t>Bundesliga 2008/09 · DFB-Pokal 2014/15 · Supercopa da Alemanha 2015</t>
   </si>
   <si>
-    <t>Dinamarca</t>
-  </si>
-  <si>
-    <t>Zehnter</t>
-  </si>
-  <si>
-    <t>LE</t>
-  </si>
-  <si>
     <t>Rogério</t>
   </si>
   <si>
@@ -658,52 +665,91 @@
     <t>Suécia</t>
   </si>
   <si>
+    <t>Meta</t>
+  </si>
+  <si>
     <t>Gerhardt</t>
   </si>
   <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Imagem</t>
+  </si>
+  <si>
+    <t>Atual</t>
+  </si>
+  <si>
     <t>Kosovo</t>
   </si>
   <si>
+    <t>Alvo</t>
+  </si>
+  <si>
     <t>Vranckx</t>
   </si>
   <si>
+    <t>Tipo</t>
+  </si>
+  <si>
     <t>Bélgica</t>
   </si>
   <si>
-    <t>Meta</t>
+    <t>Subir como campeão</t>
   </si>
   <si>
     <t>Hensel</t>
   </si>
   <si>
+    <t>Em andamento</t>
+  </si>
+  <si>
     <t>Dárdai</t>
   </si>
   <si>
-    <t>Status</t>
+    <t>Conquistar o título da 2. Bundesliga e o acesso direto</t>
   </si>
   <si>
     <t>MEI</t>
   </si>
   <si>
+    <t>subir-campeao.svg</t>
+  </si>
+  <si>
     <t>Hungria</t>
   </si>
   <si>
-    <t>Imagem</t>
-  </si>
-  <si>
-    <t>Atual</t>
-  </si>
-  <si>
-    <t>Alvo</t>
+    <t>Chegar às oitavas da DFB-Pokal</t>
+  </si>
+  <si>
+    <t>Falhou</t>
+  </si>
+  <si>
+    <t>Eliminados pelo Freiburg na 2ª fase</t>
+  </si>
+  <si>
+    <t>oitavas-pokal.svg</t>
   </si>
   <si>
     <t>ATA</t>
   </si>
   <si>
-    <t>Tipo</t>
-  </si>
-  <si>
-    <t>Subir como campeão</t>
+    <t>Encontrar um novo D'Alessandro</t>
+  </si>
+  <si>
+    <t>MEI argentino, canhoto, de 15 a 23 anos</t>
+  </si>
+  <si>
+    <t>novo-dalessandro.svg</t>
+  </si>
+  <si>
+    <t>Scouting Sul-Americano</t>
+  </si>
+  <si>
+    <t>Ter no elenco no mínimo 5 jogadores sul-americanos</t>
+  </si>
+  <si>
+    <t>scouting-sulamericano.svg</t>
   </si>
   <si>
     <t>Benedict</t>
@@ -712,43 +758,55 @@
     <t>PE</t>
   </si>
   <si>
-    <t>Em andamento</t>
+    <t>sulamericanos</t>
+  </si>
+  <si>
+    <t>Academia do Wolfsburg</t>
   </si>
   <si>
     <t>Amoura</t>
   </si>
   <si>
-    <t>Conquistar o título da 2. Bundesliga e o acesso direto</t>
+    <t>Categorias de base na Alemanha e na Argentina</t>
+  </si>
+  <si>
+    <t>academia.svg</t>
   </si>
   <si>
     <t>Argélia</t>
   </si>
   <si>
-    <t>subir-campeao.svg</t>
+    <t>Regras de contratação por janela</t>
   </si>
   <si>
     <t>Hornby</t>
   </si>
   <si>
-    <t>Chegar às oitavas da DFB-Pokal</t>
-  </si>
-  <si>
     <t>Escócia</t>
   </si>
   <si>
-    <t>Falhou</t>
+    <t>Vendeu € 10 mi: pode gastar até € 5 mi; Vendeu € 20 mi: até € 8 mi; Vendeu € 30 mi: até € 12 mi; Vendeu € 40 mi: até € 15 mi; Vendeu € 50 mi: até € 20 mi; Vendeu € 60 mi: até € 25 mi; Acima de € 60 mi: até 50% do valor das vendas</t>
+  </si>
+  <si>
+    <t>regras-transferencias.svg</t>
+  </si>
+  <si>
+    <t>Regra</t>
   </si>
   <si>
     <t>Glatzel</t>
   </si>
   <si>
-    <t>Eliminados pelo Freiburg na 2ª fase</t>
-  </si>
-  <si>
-    <t>oitavas-pokal.svg</t>
-  </si>
-  <si>
-    <t>Encontrar um novo D'Alessandro</t>
+    <t>Estilo de jogo</t>
+  </si>
+  <si>
+    <t>Inspirado no Internacional campeão da Sul-Americana 2008, no tradicional 4-3-1-2</t>
+  </si>
+  <si>
+    <t>estilo-de-jogo.svg</t>
+  </si>
+  <si>
+    <t>Regras de saída de jogadores</t>
   </si>
   <si>
     <t>Japão</t>
@@ -757,85 +815,34 @@
     <t>Besio</t>
   </si>
   <si>
-    <t>MEI argentino, canhoto, de 15 a 23 anos</t>
-  </si>
-  <si>
-    <t>novo-dalessandro.svg</t>
+    <t>Só podemos recusar propostas de compra se estivermos em 1º ou 2º lugar na Bundesliga</t>
+  </si>
+  <si>
+    <t>regras-saida.svg</t>
   </si>
   <si>
     <t>Suíça</t>
   </si>
   <si>
-    <t>Scouting Sul-Americano</t>
-  </si>
-  <si>
-    <t>Ter no elenco no mínimo 5 jogadores sul-americanos</t>
-  </si>
-  <si>
-    <t>scouting-sulamericano.svg</t>
-  </si>
-  <si>
     <t>Base</t>
   </si>
   <si>
-    <t>sulamericanos</t>
-  </si>
-  <si>
     <t>Emiliano Martínez</t>
   </si>
   <si>
-    <t>Academia do Wolfsburg</t>
-  </si>
-  <si>
     <t>Uruguai</t>
   </si>
   <si>
-    <t>Categorias de base na Alemanha e na Argentina</t>
-  </si>
-  <si>
     <t>Reforço</t>
   </si>
   <si>
-    <t>academia.svg</t>
-  </si>
-  <si>
     <t>Till Neininger</t>
   </si>
   <si>
-    <t>Regras de contratação por janela</t>
-  </si>
-  <si>
-    <t>Vendeu € 10 mi: pode gastar até € 5 mi; Vendeu € 20 mi: até € 8 mi; Vendeu € 30 mi: até € 12 mi; Vendeu € 40 mi: até € 15 mi; Vendeu € 50 mi: até € 20 mi; Vendeu € 60 mi: até € 25 mi; Acima de € 60 mi: até 50% do valor das vendas</t>
-  </si>
-  <si>
-    <t>regras-transferencias.svg</t>
-  </si>
-  <si>
-    <t>Regra</t>
-  </si>
-  <si>
     <t>Andreas Skov Olsen</t>
   </si>
   <si>
-    <t>Estilo de jogo</t>
-  </si>
-  <si>
-    <t>Inspirado no Internacional campeão da Sul-Americana 2008, no tradicional 4-3-1-2</t>
-  </si>
-  <si>
-    <t>estilo-de-jogo.svg</t>
-  </si>
-  <si>
-    <t>Regras de saída de jogadores</t>
-  </si>
-  <si>
     <t>B. Tomiak</t>
-  </si>
-  <si>
-    <t>Só podemos recusar propostas de compra se estivermos em 1º ou 2º lugar na Bundesliga</t>
-  </si>
-  <si>
-    <t>regras-saida.svg</t>
   </si>
   <si>
     <t>https://cdn.sofifa.net/players/262/119/26_120.png</t>
@@ -941,12 +948,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="10.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -955,6 +956,12 @@
       <b/>
       <sz val="11.0"/>
       <color rgb="FF2E7D32"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1014,13 +1021,13 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -1031,7 +1038,7 @@
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1040,7 +1047,7 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1319,120 +1326,120 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3"/>
+      <c r="A2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>5</v>
+      <c r="A3" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>8</v>
+      <c r="A4" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>11</v>
+      <c r="A5" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
     <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>21</v>
+      <c r="A9" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>24</v>
+      <c r="A10" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>31</v>
+      <c r="A11" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>35</v>
+      <c r="A12" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
     <row r="16">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
     <row r="18">
-      <c r="A18" s="3"/>
+      <c r="A18" s="2"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>54</v>
+      <c r="A19" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="3" t="s">
-        <v>63</v>
+      <c r="A22" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="3" t="s">
-        <v>66</v>
+      <c r="A23" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="3" t="s">
-        <v>69</v>
+      <c r="A24" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="3"/>
+      <c r="A25" s="2"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="3" t="s">
-        <v>73</v>
+      <c r="A26" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1"/>
@@ -2431,14 +2438,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>155</v>
+      <c r="A1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -3443,56 +3450,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B3" s="13"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B4" s="14"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B5" s="14"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B6" s="14"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -3518,65 +3525,65 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="F1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>3</v>
-      </c>
       <c r="G1" s="15" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B2" s="6">
         <v>1.0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F2" s="6">
         <v>0.0</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B3" s="6">
         <v>6.0</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F3" s="6">
         <v>1.9E7</v>
@@ -3584,19 +3591,19 @@
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B4" s="6">
         <v>6.0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F4" s="6">
         <v>7000000.0</v>
@@ -3604,128 +3611,128 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B5" s="6">
         <v>6.0</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F5" s="6">
         <v>0.0</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B6" s="6">
         <v>6.0</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F6" s="6">
         <v>0.0</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B7" s="6">
         <v>6.0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B8" s="6">
         <v>6.0</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B9" s="6">
         <v>7.0</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F9" s="6">
         <v>8500000.0</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B10" s="6">
         <v>7.0</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F10" s="6">
         <v>2000000.0</v>
@@ -3733,19 +3740,19 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B11" s="6">
         <v>7.0</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="F11" s="6">
         <v>2300000.0</v>
@@ -3753,19 +3760,19 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B12" s="6">
         <v>7.0</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F12" s="6">
         <v>2000000.0</v>
@@ -3773,19 +3780,19 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B13" s="6">
         <v>7.0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F13" s="6">
         <v>560000.0</v>
@@ -3810,132 +3817,132 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>4</v>
+      <c r="A1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>22</v>
+        <v>31</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>28</v>
+        <v>37</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>43</v>
+        <v>21</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>48</v>
+        <v>53</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>59</v>
+        <v>64</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B11" s="5">
         <v>2.0</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>68</v>
+      <c r="C11" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B12" s="5">
         <v>3.0</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>72</v>
+      <c r="C12" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -3945,7 +3952,7 @@
       <c r="B13" s="5">
         <v>16.0</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>75</v>
       </c>
     </row>
@@ -3956,19 +3963,19 @@
       <c r="B14" s="5">
         <v>17.0</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" s="3" t="s">
         <v>80</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -4971,28 +4978,28 @@
     <col customWidth="1" min="3" max="3" width="84.5"/>
     <col customWidth="1" min="4" max="4" width="13.0"/>
     <col customWidth="1" min="5" max="5" width="44.0"/>
-    <col customWidth="1" min="6" max="6" width="180.38"/>
+    <col customWidth="1" min="6" max="6" width="191.25"/>
     <col customWidth="1" min="7" max="26" width="8.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>19</v>
+      <c r="F1" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="2">
@@ -5000,19 +5007,19 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D2" s="7">
         <v>46302.0</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3">
@@ -5020,19 +5027,19 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D3" s="7">
         <v>46304.0</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4">
@@ -5040,19 +5047,19 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D4" s="7">
         <v>46308.0</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5">
@@ -5060,19 +5067,19 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D5" s="7">
         <v>46311.0</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6">
@@ -5080,7 +5087,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>109</v>
@@ -5100,7 +5107,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>112</v>
@@ -5112,7 +5119,7 @@
         <v>113</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8">
@@ -5120,18 +5127,35 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D8" s="11">
         <v>46322.0</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F8" s="6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D9" s="11">
+        <v>46325.0</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>126</v>
       </c>
     </row>
@@ -6124,11 +6148,12 @@
     <hyperlink r:id="rId5" ref="E6"/>
     <hyperlink r:id="rId6" ref="E7"/>
     <hyperlink r:id="rId7" ref="E8"/>
+    <hyperlink r:id="rId8" ref="E9"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId8"/>
+  <drawing r:id="rId9"/>
 </worksheet>
 </file>
 
@@ -6152,32 +6177,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>42</v>
+      <c r="A1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="2">
@@ -6188,19 +6213,19 @@
         <v>1.0</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="E2" s="6">
         <v>1.0</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H2" s="6">
         <v>4.0</v>
@@ -6217,19 +6242,19 @@
         <v>1.0</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E3" s="6">
         <v>1.0</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H3" s="6">
         <v>4.0</v>
@@ -6246,19 +6271,19 @@
         <v>1.0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E4" s="6">
         <v>2.0</v>
       </c>
       <c r="F4" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="H4" s="6">
         <v>2.0</v>
@@ -6275,10 +6300,10 @@
         <v>1.0</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E5" s="6">
         <v>3.0</v>
@@ -6287,7 +6312,7 @@
         <v>83</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H5" s="6">
         <v>2.0</v>
@@ -6304,19 +6329,19 @@
         <v>2.0</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E6" s="6">
         <v>4.0</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H6" s="6">
         <v>2.0</v>
@@ -6333,19 +6358,19 @@
         <v>2.0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E7" s="6">
         <v>5.0</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H7" s="6">
         <v>0.0</v>
@@ -6362,19 +6387,19 @@
         <v>2.0</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E8" s="6">
         <v>6.0</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H8" s="6">
         <v>1.0</v>
@@ -6391,19 +6416,19 @@
         <v>2.0</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E9" s="6">
         <v>7.0</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H9" s="6">
         <v>1.0</v>
@@ -6420,10 +6445,10 @@
         <v>3.0</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E10" s="6">
         <v>8.0</v>
@@ -6432,7 +6457,7 @@
         <v>91</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H10" s="6">
         <v>4.0</v>
@@ -6449,10 +6474,10 @@
         <v>3.0</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E11" s="6">
         <v>9.0</v>
@@ -6461,7 +6486,7 @@
         <v>92</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H11" s="6">
         <v>1.0</v>
@@ -6478,19 +6503,19 @@
         <v>3.0</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="E12" s="6">
         <v>2.0</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H12" s="6">
         <v>0.0</v>
@@ -6507,19 +6532,19 @@
         <v>3.0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E13" s="6">
         <v>10.0</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H13" s="6">
         <v>5.0</v>
@@ -6536,10 +6561,10 @@
         <v>4.0</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E14" s="6">
         <v>11.0</v>
@@ -6548,7 +6573,7 @@
         <v>98</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H14" s="6">
         <v>3.0</v>
@@ -6565,10 +6590,10 @@
         <v>4.0</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E15" s="6">
         <v>12.0</v>
@@ -6577,7 +6602,7 @@
         <v>99</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H15" s="6">
         <v>1.0</v>
@@ -6594,19 +6619,19 @@
         <v>4.0</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E16" s="6">
         <v>13.0</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H16" s="6">
         <v>1.0</v>
@@ -6623,19 +6648,19 @@
         <v>5.0</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E17" s="6">
         <v>14.0</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H17" s="6">
         <v>1.0</v>
@@ -6652,19 +6677,19 @@
         <v>5.0</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E18" s="6">
         <v>15.0</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H18" s="6">
         <v>2.0</v>
@@ -6681,10 +6706,10 @@
         <v>5.0</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E19" s="6">
         <v>16.0</v>
@@ -6693,7 +6718,7 @@
         <v>106</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H19" s="6">
         <v>2.0</v>
@@ -6710,19 +6735,19 @@
         <v>6.0</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E20" s="6">
         <v>17.0</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H20" s="6">
         <v>1.0</v>
@@ -6739,19 +6764,19 @@
         <v>6.0</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E21" s="6">
         <v>18.0</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H21" s="6">
         <v>2.0</v>
@@ -6768,19 +6793,19 @@
         <v>6.0</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E22" s="6">
         <v>19.0</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H22" s="6">
         <v>2.0</v>
@@ -6797,10 +6822,10 @@
         <v>7.0</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E23" s="6">
         <v>20.0</v>
@@ -6809,7 +6834,7 @@
         <v>83</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H23" s="6">
         <v>0.0</v>
@@ -6826,19 +6851,19 @@
         <v>7.0</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E24" s="6">
         <v>21.0</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H24" s="6">
         <v>0.0</v>
@@ -6855,19 +6880,19 @@
         <v>7.0</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E25" s="6">
         <v>22.0</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H25" s="6">
         <v>3.0</v>
@@ -6884,19 +6909,19 @@
         <v>7.0</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E26" s="6">
         <v>23.0</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H26" s="6">
         <v>0.0</v>
@@ -6906,20 +6931,120 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="D27" s="5"/>
-      <c r="G27" s="5"/>
+      <c r="A27" s="6">
+        <v>26.0</v>
+      </c>
+      <c r="B27" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E27" s="6">
+        <v>24.0</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H27" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="I27" s="6">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="D28" s="5"/>
-      <c r="G28" s="5"/>
+      <c r="A28" s="6">
+        <v>27.0</v>
+      </c>
+      <c r="B28" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" s="6">
+        <v>25.0</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H28" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="I28" s="6">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="D29" s="5"/>
-      <c r="G29" s="5"/>
+      <c r="A29" s="6">
+        <v>28.0</v>
+      </c>
+      <c r="B29" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E29" s="6">
+        <v>26.0</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H29" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="I29" s="6">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="D30" s="5"/>
-      <c r="G30" s="5"/>
+      <c r="A30" s="6">
+        <v>29.0</v>
+      </c>
+      <c r="B30" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E30" s="6">
+        <v>27.0</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H30" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="I30" s="6">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="D31" s="5"/>
@@ -10831,17 +10956,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>116</v>
+      <c r="A1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="2">
@@ -10852,10 +10977,10 @@
         <v>33.0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3">
@@ -10866,10 +10991,10 @@
         <v>38.0</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4">
@@ -10880,7 +11005,7 @@
         <v>50.0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>123</v>
@@ -10897,7 +11022,7 @@
         <v>123</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6">
@@ -10908,7 +11033,7 @@
         <v>17.0</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>123</v>
@@ -10922,7 +11047,7 @@
         <v>42.0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>123</v>
@@ -10947,10 +11072,10 @@
         <v>86.0</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10">
@@ -10961,7 +11086,7 @@
         <v>28.0</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>123</v>
@@ -10975,7 +11100,7 @@
         <v>53.0</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12">
@@ -10989,7 +11114,7 @@
         <v>123</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -11003,7 +11128,7 @@
         <v>123</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -11014,10 +11139,10 @@
         <v>8.0</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15">
@@ -11028,7 +11153,7 @@
         <v>80.0</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>123</v>
@@ -11042,10 +11167,10 @@
         <v>75.0</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17">
@@ -11056,10 +11181,10 @@
         <v>73.0</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18">
@@ -11070,10 +11195,10 @@
         <v>28.0</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19">
@@ -11084,7 +11209,7 @@
         <v>35.0</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>123</v>
@@ -11098,10 +11223,10 @@
         <v>40.0</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -11112,10 +11237,10 @@
         <v>88.0</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -11126,10 +11251,10 @@
         <v>28.0</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -11140,10 +11265,10 @@
         <v>27.0</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -11154,10 +11279,10 @@
         <v>37.0</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -11171,7 +11296,7 @@
         <v>123</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -11182,10 +11307,10 @@
         <v>56.0</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
@@ -11196,10 +11321,10 @@
         <v>69.0</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -11210,10 +11335,10 @@
         <v>4.0</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -11224,10 +11349,10 @@
         <v>7.0</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -11238,10 +11363,10 @@
         <v>39.0</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
@@ -11252,10 +11377,10 @@
         <v>59.0</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
@@ -11266,10 +11391,10 @@
         <v>82.0</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
@@ -11280,10 +11405,10 @@
         <v>47.0</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
@@ -11294,10 +11419,10 @@
         <v>3.0</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
@@ -11308,10 +11433,10 @@
         <v>63.0</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
@@ -11322,10 +11447,10 @@
         <v>74.0</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
@@ -11336,10 +11461,10 @@
         <v>82.0</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
@@ -11353,7 +11478,7 @@
         <v>123</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
@@ -11367,7 +11492,7 @@
         <v>123</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
@@ -11378,10 +11503,10 @@
         <v>71.0</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
@@ -11392,10 +11517,10 @@
         <v>20.0</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
@@ -11406,7 +11531,7 @@
         <v>84.0</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>123</v>
@@ -11420,10 +11545,10 @@
         <v>41.0</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
@@ -11434,10 +11559,10 @@
         <v>49.0</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
@@ -11448,16 +11573,65 @@
         <v>55.0</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="6">
+        <v>26.0</v>
+      </c>
+      <c r="B46" s="6">
+        <v>55.0</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="6">
+        <v>27.0</v>
+      </c>
+      <c r="B47" s="6">
+        <v>64.0</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="6">
+        <v>29.0</v>
+      </c>
+      <c r="B48" s="6">
+        <v>21.0</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="6">
+        <v>29.0</v>
+      </c>
+      <c r="B49" s="6">
+        <v>34.0</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
     <row r="52" ht="15.75" customHeight="1"/>
@@ -12432,66 +12606,66 @@
   </cols>
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>134</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="B2" s="6">
         <v>1.0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D2" s="6">
-        <v>23.0</v>
+        <v>27.0</v>
       </c>
       <c r="E2" s="6">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="F2" s="6">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="G2" s="6">
         <v>4.0</v>
       </c>
       <c r="H2" s="6">
-        <v>40.0</v>
+        <v>44.0</v>
       </c>
       <c r="I2" s="6">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="B3" s="6">
         <v>2.0</v>
@@ -12500,138 +12674,138 @@
         <v>98</v>
       </c>
       <c r="D3" s="6">
-        <v>23.0</v>
+        <v>27.0</v>
       </c>
       <c r="E3" s="6">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="F3" s="6">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G3" s="6">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="H3" s="6">
-        <v>35.0</v>
+        <v>39.0</v>
       </c>
       <c r="I3" s="6">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="B4" s="6">
         <v>3.0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D4" s="6">
-        <v>23.0</v>
+        <v>27.0</v>
       </c>
       <c r="E4" s="6">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="F4" s="6">
         <v>6.0</v>
       </c>
       <c r="G4" s="6">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H4" s="6">
-        <v>30.0</v>
+        <v>34.0</v>
       </c>
       <c r="I4" s="6">
-        <v>23.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="B5" s="6">
         <v>4.0</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="D5" s="6">
-        <v>23.0</v>
+        <v>28.0</v>
       </c>
       <c r="E5" s="6">
+        <v>12.0</v>
+      </c>
+      <c r="F5" s="6">
         <v>7.0</v>
       </c>
-      <c r="F5" s="6">
-        <v>14.0</v>
-      </c>
       <c r="G5" s="6">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
       <c r="H5" s="6">
-        <v>34.0</v>
+        <v>36.0</v>
       </c>
       <c r="I5" s="6">
-        <v>25.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="B6" s="6">
         <v>5.0</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="D6" s="6">
-        <v>23.0</v>
+        <v>27.0</v>
       </c>
       <c r="E6" s="6">
+        <v>11.0</v>
+      </c>
+      <c r="F6" s="6">
         <v>10.0</v>
       </c>
-      <c r="F6" s="6">
-        <v>5.0</v>
-      </c>
       <c r="G6" s="6">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H6" s="6">
-        <v>30.0</v>
+        <v>38.0</v>
       </c>
       <c r="I6" s="6">
-        <v>25.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="B7" s="6">
         <v>6.0</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D7" s="6">
-        <v>23.0</v>
+        <v>28.0</v>
       </c>
       <c r="E7" s="6">
         <v>8.0</v>
       </c>
       <c r="F7" s="6">
-        <v>10.0</v>
+        <v>16.0</v>
       </c>
       <c r="G7" s="6">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="H7" s="6">
+        <v>41.0</v>
+      </c>
+      <c r="I7" s="6">
         <v>33.0</v>
-      </c>
-      <c r="I7" s="6">
-        <v>29.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -13643,62 +13817,62 @@
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4">
@@ -13706,279 +13880,279 @@
         <v>161</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>183</v>
-      </c>
       <c r="E10" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>202</v>
-      </c>
       <c r="E12" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>204</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>204</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>207</v>
-      </c>
       <c r="D18" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -13986,128 +14160,128 @@
         <v>123</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="6" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="6" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="6" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>240</v>
+        <v>259</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="F32" s="6">
         <v>3.0</v>
@@ -14115,16 +14289,16 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="6" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="F33" s="6">
         <v>6.0</v>
@@ -14132,70 +14306,70 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="6" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="6" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="6" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="F36" s="6">
         <v>7.0</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="F37" s="6">
         <v>7.0</v>
@@ -14203,16 +14377,16 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="F38" s="6">
         <v>7.0</v>
@@ -14220,16 +14394,16 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="F39" s="6">
         <v>7.0</v>
@@ -15541,94 +15715,94 @@
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="12" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C2" s="6">
         <v>10.0</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C3" s="6">
         <v>9.0</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C4" s="6">
         <v>28.0</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5">
@@ -15636,72 +15810,72 @@
         <v>186</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C5" s="6">
         <v>20.0</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C6" s="6">
         <v>66.0</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C7" s="6">
         <v>3.0</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8">
-      <c r="F8" s="3"/>
+      <c r="F8" s="2"/>
       <c r="G8" s="5"/>
     </row>
     <row r="9">
@@ -16913,96 +17087,96 @@
   <sheetData>
     <row r="1" ht="19.5" customHeight="1">
       <c r="A1" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="B1" s="12" t="s">
-        <v>216</v>
-      </c>
       <c r="C1" s="12" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>223</v>
-      </c>
       <c r="I1" s="6" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>231</v>
-      </c>
       <c r="H2" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="E5" s="6">
         <v>2.0</v>
@@ -17011,72 +17185,72 @@
         <v>5.0</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="6" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="6" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="6" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
